--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -697,7 +697,11 @@
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -786,7 +790,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -879,7 +887,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -968,7 +980,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1057,7 +1073,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1146,7 +1166,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1235,7 +1259,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1324,7 +1352,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1413,7 +1445,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1502,7 +1538,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1595,7 +1635,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1684,7 +1728,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1773,7 +1821,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1866,7 +1918,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1959,7 +2015,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2048,7 +2108,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2141,7 +2205,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2234,7 +2302,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2323,7 +2395,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2412,7 +2488,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2501,7 +2581,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2590,7 +2674,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2679,7 +2767,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2768,7 +2860,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2857,7 +2953,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2946,7 +3046,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -3035,7 +3139,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -3043,12 +3151,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Krishana Phoschem Limited</t>
+          <t>Vadilal Industries Limited</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3062,7 +3170,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>5895</v>
+        <v>5572</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -3073,10 +3181,10 @@
         <v>4</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>188.94</v>
+        <v>7781</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>188.94</v>
+        <v>7781</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -3087,7 +3195,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>75.34999999999999</v>
+        <v>56.81</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>3.95</v>
@@ -3097,21 +3205,21 @@
       </c>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>8.9</v>
+        <v>40.4</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3124,7 +3232,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -3132,12 +3244,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Vadilal Industries Limited</t>
+          <t>Kapston Services Limited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3151,21 +3263,21 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5572</v>
+        <v>1791</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7781</v>
+        <v>585.1</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7781</v>
+        <v>585.1</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -3176,7 +3288,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>56.81</v>
+        <v>136.39</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>3.95</v>
@@ -3186,17 +3298,17 @@
       </c>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n">
-        <v>52.9</v>
+        <v>132.4</v>
       </c>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n">
-        <v>219</v>
+        <v>30.5</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>156</v>
+        <v>28.1</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>40.4</v>
+        <v>8.5</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
@@ -3213,7 +3325,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -3221,26 +3337,26 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Kapston Services Limited</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1791</v>
+        <v>1399</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -3248,61 +3364,69 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>585.1</v>
+        <v>583</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>585.1</v>
+        <v>583</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>136.39</v>
+        <v>100.58</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P31" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="Q31" s="2" t="n">
-        <v>132.4</v>
-      </c>
-      <c r="R31" s="2" t="n"/>
+        <v>96.5</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>104.4</v>
+      </c>
       <c r="S31" s="2" t="n">
-        <v>30.5</v>
+        <v>44</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>28.1</v>
+        <v>44</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr"/>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -3310,12 +3434,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>COMSYN</t>
+          <t>KINGFA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Commercial Syn Bags Limited</t>
+          <t>Kingfa Science &amp; Technology (India) Limited</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3329,7 +3453,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1163</v>
+        <v>7955</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -3340,10 +3464,10 @@
         <v>5</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>282.66</v>
+        <v>6028.5</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>282.66</v>
+        <v>6028.5</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -3354,7 +3478,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>108.34</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="N32" s="2" t="n">
         <v>3.95</v>
@@ -3364,21 +3488,21 @@
       </c>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n">
-        <v>104.4</v>
+        <v>63.3</v>
       </c>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n">
-        <v>29.7</v>
+        <v>225</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>6.1</v>
+        <v>21.6</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -3391,7 +3515,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -3399,92 +3527,92 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>KENNAMET</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>Kennametal India Limited</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>SME</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1399</v>
+        <v>7722</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>583</v>
+        <v>3674.1</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>583</v>
+        <v>3674.1</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>100.58</v>
+        <v>48.38</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>4.03</v>
+        <v>26.31</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+        <v>26.99</v>
+      </c>
+      <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="R33" s="2" t="n">
-        <v>104.4</v>
-      </c>
+        <v>22.1</v>
+      </c>
+      <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr"/>
+          <t>Sep 2022</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3492,12 +3620,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KINGFA</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kingfa Science &amp; Technology (India) Limited</t>
+          <t>KSH International Limited</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3511,52 +3639,52 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7955</v>
+        <v>6969</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6028.5</v>
+        <v>1028.6</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6028.5</v>
+        <v>1028.6</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>67.20999999999999</v>
+        <v>189.75</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3.95</v>
+        <v>-1.26</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>4.31</v>
+        <v>-0.63</v>
       </c>
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n">
-        <v>63.3</v>
+        <v>191</v>
       </c>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>21.6</v>
+        <v>17.1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
@@ -3573,7 +3701,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -3581,12 +3713,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>KENNAMET</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Kennametal India Limited</t>
+          <t>SG Mart Limited</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3600,21 +3732,21 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>7722</v>
+        <v>9274</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3674.1</v>
+        <v>747.15</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3674.1</v>
+        <v>747.15</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -3625,27 +3757,27 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>48.38</v>
+        <v>108.64</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>26.31</v>
+        <v>1.74</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>26.99</v>
+        <v>2.1</v>
       </c>
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n">
-        <v>22.1</v>
+        <v>106.9</v>
       </c>
       <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
@@ -3659,10 +3791,14 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr"/>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3670,12 +3806,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>COMSYN</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>KSH International Limited</t>
+          <t>Commercial Syn Bags Limited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3689,7 +3825,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>6969</v>
+        <v>1163</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -3697,48 +3833,48 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1028.6</v>
+        <v>282.66</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1028.6</v>
+        <v>282.66</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>189.75</v>
+        <v>108.34</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.26</v>
+        <v>3.95</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>-0.63</v>
+        <v>4.31</v>
       </c>
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n">
-        <v>191</v>
+        <v>104.4</v>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n">
-        <v>130</v>
+        <v>29.7</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>17.1</v>
+        <v>6.1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -3751,7 +3887,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3759,12 +3899,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SG Mart Limited</t>
+          <t>Shilpa Medicare Limited</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3774,11 +3914,11 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>9274</v>
+        <v>16077</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -3789,41 +3929,45 @@
         <v>8</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>747.15</v>
+        <v>807.05</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>747.15</v>
+        <v>819.7</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>108.64</v>
+        <v>78.12</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.74</v>
+        <v>3.95</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P37" s="2" t="n"/>
+        <v>4.31</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>12.35</v>
+      </c>
       <c r="Q37" s="2" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="R37" s="2" t="n"/>
+        <v>74.2</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>65.8</v>
+      </c>
       <c r="S37" s="2" t="n">
-        <v>125</v>
+        <v>298</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>120</v>
+        <v>244</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>4.2</v>
+        <v>22.1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
@@ -3840,7 +3984,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3848,12 +3996,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>KDDL</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited</t>
+          <t>KDDL Limited</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3863,11 +4011,11 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>16077</v>
+        <v>4834</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -3878,21 +4026,21 @@
         <v>8</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>807.05</v>
+        <v>3945.9</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>819.7</v>
+        <v>3945.9</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>78.12</v>
+        <v>56.61</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>3.95</v>
@@ -3900,23 +4048,19 @@
       <c r="O38" s="2" t="n">
         <v>4.31</v>
       </c>
-      <c r="P38" s="2" t="n">
-        <v>12.35</v>
-      </c>
+      <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="R38" s="2" t="n">
-        <v>65.8</v>
-      </c>
+        <v>52.7</v>
+      </c>
+      <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n">
-        <v>298</v>
+        <v>151</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>22.1</v>
+        <v>3.4</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
@@ -3933,7 +4077,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3941,12 +4089,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>KDDL</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>KDDL Limited</t>
+          <t>Pearl Global Industries Limited</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3960,32 +4108,32 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>4834</v>
+        <v>11430</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3945.9</v>
+        <v>2464.9</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3945.9</v>
+        <v>2480.4</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>56.61</v>
+        <v>97.41</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>3.95</v>
@@ -3995,17 +4143,17 @@
       </c>
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n">
-        <v>52.7</v>
+        <v>93.5</v>
       </c>
       <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n">
-        <v>151</v>
+        <v>304</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>146</v>
+        <v>271</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>3.4</v>
+        <v>12.2</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
@@ -4022,7 +4170,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -4030,12 +4182,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
+          <t>Sudeep Pharma Limited</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4045,60 +4197,64 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Chemicals</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2611</v>
+        <v>12487</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5403</v>
+        <v>1105.55</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5418</v>
+        <v>1108.4</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>12.85</v>
+        <v>42.81</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>3.19</v>
+        <v>-1.41</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="P40" s="2" t="n"/>
+        <v>-0.85</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>6.68</v>
+      </c>
       <c r="Q40" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="R40" s="2" t="n"/>
+        <v>44.2</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>36.1</v>
+      </c>
       <c r="S40" s="2" t="n">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4111,7 +4267,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -4119,12 +4279,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Limited</t>
+          <t>Happy Forgings Limited</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4138,24 +4298,24 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>11430</v>
+        <v>19721</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2464.9</v>
+        <v>2007.6</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2480.4</v>
+        <v>2022.7</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.75</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -4163,7 +4323,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>97.41</v>
+        <v>113.31</v>
       </c>
       <c r="N41" s="2" t="n">
         <v>3.95</v>
@@ -4173,17 +4333,17 @@
       </c>
       <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n">
-        <v>93.5</v>
+        <v>109.4</v>
       </c>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>12.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
@@ -4200,7 +4360,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -4208,12 +4372,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Sudeep Pharma Limited</t>
+          <t>Rajputana Stainless Limited</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4223,64 +4387,60 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Nifty Chemicals</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>12487</v>
+        <v>1382</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1105.55</v>
+        <v>166.77</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1108.4</v>
+        <v>166.77</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>42.81</v>
+        <v>47.54</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.41</v>
+        <v>11.16</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="P42" s="2" t="n">
-        <v>6.68</v>
-      </c>
+        <v>11.94</v>
+      </c>
+      <c r="P42" s="2" t="n"/>
       <c r="Q42" s="2" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="R42" s="2" t="n">
-        <v>36.1</v>
-      </c>
+        <v>36.4</v>
+      </c>
+      <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n">
-        <v>185</v>
+        <v>58</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -4293,7 +4453,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -4301,12 +4465,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited</t>
+          <t>GSP Crop Science Limited</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4320,52 +4484,52 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>19721</v>
+        <v>2774</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>591.7</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>597.5</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="N43" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>2007.6</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>2022.7</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>113.31</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>3.95</v>
-      </c>
       <c r="O43" s="2" t="n">
-        <v>4.31</v>
+        <v>12.8</v>
       </c>
       <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="n">
-        <v>109.4</v>
+        <v>54.1</v>
       </c>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
@@ -4382,7 +4546,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -4390,12 +4558,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>Krishana Phoschem Limited</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4409,21 +4577,21 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1382</v>
+        <v>5895</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>166.77</v>
+        <v>188.94</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>166.77</v>
+        <v>188.94</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -4434,27 +4602,27 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>47.54</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>11.16</v>
+        <v>3.95</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>11.94</v>
+        <v>4.31</v>
       </c>
       <c r="P44" s="2" t="n"/>
       <c r="Q44" s="2" t="n">
-        <v>36.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n">
-        <v>58</v>
+        <v>196</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>16</v>
+        <v>8.9</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
@@ -4471,7 +4639,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -4479,12 +4651,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>GSP Crop Science Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4498,56 +4670,56 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>2774</v>
+        <v>2611</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>591.7</v>
+        <v>5403</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>597.5</v>
+        <v>5418</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-0.97</v>
+        <v>-0.28</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>66.09</v>
+        <v>7.34</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>12</v>
+        <v>1.94</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>12.8</v>
+        <v>2.06</v>
       </c>
       <c r="P45" s="2" t="n"/>
       <c r="Q45" s="2" t="n">
-        <v>54.1</v>
+        <v>5.4</v>
       </c>
       <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>1</v>
+        <v>7.1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -4560,7 +4732,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -4595,7 +4771,7 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>3435.5</v>
@@ -4649,7 +4825,11 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Y46"/>
@@ -4734,7 +4914,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2673 screened -&gt; 136 at ATH -&gt; 133 outperforming -&gt; 90 record PAT -&gt; 45 in mcap band</t>
+          <t>2673 screened -&gt; 148 at ATH -&gt; 140 outperforming -&gt; 90 record PAT -&gt; 45 in mcap band</t>
         </is>
       </c>
     </row>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$Y$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AA$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,12 +79,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -449,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -467,16 +473,18 @@
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,65 +550,75 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>3M Return %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>6M Return %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>TTM Return %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Nifty 500 %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Nifty TM %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Sector/SME %</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Alpha vs N500 pp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Alpha vs Sector/SME pp</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TTM PAT (Rs Cr)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Prior Peak PAT</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>PAT vs Peak %</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Latest Period</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>New This Week</t>
         </is>
@@ -622,7 +640,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SME</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -656,240 +674,262 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>107.41</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>156.79</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>152.8</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="T2" s="2" t="n">
         <v>160.6</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="U2" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="V2" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="W2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>MANINDS</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Man Industries (India) Limited</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>4496</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>KESAR</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>KESAR INDIA LIMITED</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>3956</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>599.45</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>601.4</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="N3" s="2" t="n">
+      <c r="I3" s="3" t="n">
+        <v>1266.1</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1284.85</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>94.78</v>
+      </c>
+      <c r="P3" s="3" t="n">
         <v>4.03</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="Q3" s="3" t="n">
         <v>4.42</v>
       </c>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="R3" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>MANORAMA</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Manorama Industries Limited</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Nifty FMCG</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>10965</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>AFCOM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Afcom Holdings Limited</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>4311</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1737.1</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1737.1</v>
-      </c>
-      <c r="K4" s="2" t="n">
+      <c r="I4" s="3" t="n">
+        <v>1502.05</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1502.05</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>26.21</v>
-      </c>
-      <c r="N4" s="2" t="n">
+      <c r="M4" s="3" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>4.03</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="Q4" s="3" t="n">
         <v>4.42</v>
       </c>
-      <c r="P4" s="2" t="n">
-        <v>-11.05</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>258</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>226</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="R4" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -899,12 +939,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KMEW</t>
+          <t>MANINDS</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Knowledge Marine &amp; Engineering Works Limited</t>
+          <t>Man Industries (India) Limited</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -918,164 +958,180 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6926</v>
+        <v>4496</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2730.8</v>
+        <v>599.45</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2730.8</v>
+        <v>601.4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>227.22</v>
+        <v>7.02</v>
       </c>
       <c r="N5" s="2" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="P5" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>4.42</v>
-      </c>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n">
-        <v>223.2</v>
       </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>80</v>
-      </c>
+        <v>47.2</v>
+      </c>
+      <c r="T5" s="2" t="n"/>
       <c r="U5" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+        <v>204</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>RPEL</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Raghav Productivity Enhancers Limited</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6585</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>KHAZANCHI</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Khazanchi Jewellers Limited</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>1388.8</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1388.8</v>
-      </c>
-      <c r="K6" s="2" t="n">
+      <c r="I6" s="3" t="n">
+        <v>792.45</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>792.45</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>130.81</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1141,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Marine Electricals (India) Limited</t>
+          <t>Manorama Industries Limited</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1100,73 +1156,83 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty FMCG</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>5188</v>
+        <v>10965</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>371.2</v>
+        <v>1737.1</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>371.2</v>
+        <v>1737.1</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>116.08</v>
+        <v>33.05</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.95</v>
+        <v>23.17</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P7" s="2" t="n"/>
+        <v>26.21</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>4.03</v>
+      </c>
       <c r="Q7" s="2" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="R7" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>-11.05</v>
+      </c>
       <c r="S7" s="2" t="n">
-        <v>66</v>
+        <v>22.2</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>60</v>
+        <v>37.3</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+        <v>258</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1178,12 +1244,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>KMEW</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Stylam Industries Limited</t>
+          <t>Knowledge Marine &amp; Engineering Works Limited</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1197,7 +1263,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6172</v>
+        <v>6926</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1205,61 +1271,67 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3595.7</v>
+        <v>2730.8</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3651.2</v>
+        <v>2730.8</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-1.52</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>115.13</v>
+        <v>38.07</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3.95</v>
+        <v>60.83</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P8" s="2" t="n"/>
+        <v>227.22</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>4.03</v>
+      </c>
       <c r="Q8" s="2" t="n">
-        <v>111.2</v>
+        <v>4.42</v>
       </c>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>150</v>
-      </c>
+        <v>223.2</v>
+      </c>
+      <c r="T8" s="2" t="n"/>
       <c r="U8" s="2" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+        <v>132</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1271,12 +1343,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Azad Engineering Limited</t>
+          <t>Raghav Productivity Enhancers Limited</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1290,7 +1362,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>17552</v>
+        <v>6585</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1301,10 +1373,10 @@
         <v>1</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2665.1</v>
+        <v>1388.8</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2665.1</v>
+        <v>1388.8</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -1315,44 +1387,50 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>75.48999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="N9" s="2" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>130.81</v>
+      </c>
+      <c r="P9" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n">
-        <v>71.5</v>
       </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>134</v>
-      </c>
+        <v>126.9</v>
+      </c>
+      <c r="T9" s="2" t="n"/>
       <c r="U9" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+        <v>63</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1364,12 +1442,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>STEELCAS</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Steelcast Limited</t>
+          <t>Marine Electricals (India) Limited</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1383,7 +1461,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3561</v>
+        <v>5188</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1394,10 +1472,10 @@
         <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>354.15</v>
+        <v>371.2</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>354.15</v>
+        <v>371.2</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -1408,44 +1486,50 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>71.09</v>
+        <v>69.7</v>
       </c>
       <c r="N10" s="2" t="n">
+        <v>97.23</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>116.08</v>
+      </c>
+      <c r="P10" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n">
-        <v>67.09999999999999</v>
       </c>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>91</v>
-      </c>
+        <v>112.1</v>
+      </c>
+      <c r="T10" s="2" t="n"/>
       <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
+        <v>66</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1457,12 +1541,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>GHCL Textiles Limited</t>
+          <t>Stylam Industries Limited</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1476,7 +1560,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1129</v>
+        <v>6172</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1487,58 +1571,64 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>121.26</v>
+        <v>3595.7</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>121.59</v>
+        <v>3651.2</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-0.27</v>
+        <v>-1.52</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>55.52</v>
+        <v>41.17</v>
       </c>
       <c r="N11" s="2" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>115.13</v>
+      </c>
+      <c r="P11" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n">
-        <v>51.6</v>
       </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>71</v>
-      </c>
+        <v>111.2</v>
+      </c>
+      <c r="T11" s="2" t="n"/>
       <c r="U11" s="2" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
+        <v>169</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1550,12 +1640,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences Limited</t>
+          <t>Azad Engineering Limited</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1565,11 +1655,11 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>17025</v>
+        <v>17552</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1580,62 +1670,64 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1374.6</v>
+        <v>2665.1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1393.6</v>
+        <v>2665.1</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>43.43</v>
+        <v>22.11</v>
       </c>
       <c r="N12" s="2" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="P12" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>4.31</v>
       </c>
-      <c r="P12" s="2" t="n">
-        <v>12.35</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n">
-        <v>603</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>565</v>
-      </c>
+        <v>71.5</v>
+      </c>
+      <c r="T12" s="2" t="n"/>
       <c r="U12" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
+        <v>140</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1647,12 +1739,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>JGCHEM</t>
+          <t>STEELCAS</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>J.G.Chemicals Limited</t>
+          <t>Steelcast Limited</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1666,7 +1758,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2375</v>
+        <v>3561</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1677,153 +1769,169 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>613</v>
+        <v>354.15</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>622.35</v>
+        <v>354.15</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25.68</v>
+        <v>23.61</v>
       </c>
       <c r="N13" s="2" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="P13" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n">
-        <v>21.7</v>
       </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>69</v>
-      </c>
+        <v>67.09999999999999</v>
+      </c>
+      <c r="T13" s="2" t="n"/>
       <c r="U13" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
+        <v>91</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y13" s="2" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>THELEELA</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>17034</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>CFF</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>CFF FLUID CONTROL LIMITED</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2142</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>508.45</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>518</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>16.24</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1021.35</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>1023.7</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1833,92 +1941,94 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>GHCL Textiles Limited</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>SME</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2202</v>
+        <v>1129</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>852</v>
+        <v>121.26</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>852</v>
+        <v>121.59</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>176.04</v>
+        <v>35.53</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>4.03</v>
+        <v>57.26</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>4.42</v>
+        <v>55.52</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>-3.8</v>
+        <v>3.95</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>179.8</v>
-      </c>
+        <v>4.31</v>
+      </c>
+      <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>27</v>
-      </c>
+        <v>51.6</v>
+      </c>
+      <c r="T15" s="2" t="n"/>
       <c r="U15" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+        <v>96</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1930,92 +2040,98 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>Alivus Life Sciences Limited</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SME</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2065</v>
+        <v>17025</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>950.25</v>
+        <v>1374.6</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>967.6</v>
+        <v>1393.6</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-1.79</v>
+        <v>-1.36</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>137.56</v>
+        <v>29.18</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.03</v>
+        <v>48.98</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>4.42</v>
+        <v>43.43</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>-3.8</v>
+        <v>3.95</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>133.5</v>
+        <v>4.31</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>141.4</v>
+        <v>12.35</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>29</v>
+        <v>39.5</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>23</v>
+        <v>31.1</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
+        <v>603</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>565</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2027,12 +2143,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>DIVGIITTS</t>
+          <t>JGCHEM</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Divgi Torqtransfer Systems Limited</t>
+          <t>J.G.Chemicals Limited</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2046,69 +2162,75 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3979</v>
+        <v>2375</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1301.05</v>
+        <v>613</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1301.05</v>
+        <v>622.35</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>101.34</v>
+        <v>47.3</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>4.03</v>
+        <v>52.96</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="P17" s="2" t="n"/>
+        <v>25.68</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>3.95</v>
+      </c>
       <c r="Q17" s="2" t="n">
-        <v>97.3</v>
+        <v>4.31</v>
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="T17" s="2" t="n">
-        <v>51</v>
-      </c>
+        <v>21.7</v>
+      </c>
+      <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2120,12 +2242,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SPR Auto Technologies Limited</t>
+          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2135,77 +2257,79 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nifty Auto</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>19789</v>
+        <v>17034</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4487.7</v>
+        <v>508.45</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4524.4</v>
+        <v>518</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.84</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>83.5</v>
+        <v>24.03</v>
       </c>
       <c r="N18" s="2" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="P18" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>4.31</v>
       </c>
-      <c r="P18" s="2" t="n">
-        <v>21.08</v>
-      </c>
-      <c r="Q18" s="2" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>62.4</v>
-      </c>
+      <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n">
-        <v>575</v>
-      </c>
-      <c r="T18" s="2" t="n">
-        <v>562</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="T18" s="2" t="n"/>
       <c r="U18" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+        <v>444</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y18" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2217,26 +2341,26 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The Karnataka Bank Limited</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Nifty Financial Services</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>11714</v>
+        <v>2202</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -2247,62 +2371,68 @@
         <v>3</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>309.65</v>
+        <v>852</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>313.7</v>
+        <v>852</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-1.29</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>82.26000000000001</v>
+        <v>126.75</v>
       </c>
       <c r="N19" s="2" t="n">
+        <v>182.07</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>176.04</v>
+      </c>
+      <c r="P19" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="P19" s="2" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="Q19" s="2" t="n">
-        <v>78.2</v>
-      </c>
       <c r="R19" s="2" t="n">
-        <v>82.7</v>
+        <v>-3.8</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>1437</v>
+        <v>172</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>1341</v>
+        <v>179.8</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
+        <v>31.5</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="W19" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2314,26 +2444,26 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>MONOLITH</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KRN Heat Exchanger and Refrigeration Limited</t>
+          <t>MONOLITH</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>9611</v>
+        <v>2065</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -2341,16 +2471,16 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1398.4</v>
+        <v>950.25</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1398.4</v>
+        <v>967.6</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2358,44 +2488,54 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>58.99</v>
+        <v>81.73</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.95</v>
+        <v>105.55</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P20" s="2" t="n"/>
+        <v>137.56</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>4.03</v>
+      </c>
       <c r="Q20" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="R20" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="S20" s="2" t="n">
-        <v>97</v>
+        <v>133.5</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>76</v>
+        <v>141.4</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2407,12 +2547,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>DIVGIITTS</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ram Ratna Wires Limited</t>
+          <t>Divgi Torqtransfer Systems Limited</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2426,7 +2566,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4435</v>
+        <v>3979</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -2437,10 +2577,10 @@
         <v>3</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>475.05</v>
+        <v>1301.05</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>475.05</v>
+        <v>1301.05</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -2451,44 +2591,50 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>39.18</v>
+        <v>95.94</v>
       </c>
       <c r="N21" s="2" t="n">
+        <v>74.73999999999999</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>101.34</v>
+      </c>
+      <c r="P21" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>4.42</v>
-      </c>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n">
-        <v>35.1</v>
       </c>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="T21" s="2" t="n">
-        <v>109</v>
-      </c>
+        <v>97.3</v>
+      </c>
+      <c r="T21" s="2" t="n"/>
       <c r="U21" s="2" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
+        <v>63</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X21" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2500,12 +2646,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>SPR Auto Technologies Limited</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2515,73 +2661,83 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Auto</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>12967</v>
+        <v>19789</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1940.8</v>
+        <v>4487.7</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1965.3</v>
+        <v>4524.4</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-1.25</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>131.67</v>
+        <v>34.07</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.03</v>
+        <v>42.2</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="P22" s="2" t="n"/>
+        <v>83.5</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>3.95</v>
+      </c>
       <c r="Q22" s="2" t="n">
-        <v>127.6</v>
-      </c>
-      <c r="R22" s="2" t="n"/>
+        <v>4.31</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>21.08</v>
+      </c>
       <c r="S22" s="2" t="n">
-        <v>134</v>
+        <v>79.5</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>113</v>
+        <v>62.4</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+        <v>575</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2593,12 +2749,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SENORES</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Senores Pharmaceuticals Limited</t>
+          <t>The Karnataka Bank Limited</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2608,28 +2764,28 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Financial Services</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>6805</v>
+        <v>11714</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1491.4</v>
+        <v>309.65</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1492.4</v>
+        <v>313.7</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.29</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -2637,44 +2793,54 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>119.21</v>
+        <v>25.82</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3.95</v>
+        <v>52.75</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P23" s="2" t="n"/>
+        <v>82.26000000000001</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>4.03</v>
+      </c>
       <c r="Q23" s="2" t="n">
-        <v>115.3</v>
-      </c>
-      <c r="R23" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="S23" s="2" t="n">
-        <v>131</v>
+        <v>78.2</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>122</v>
+        <v>82.7</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+        <v>1437</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>1341</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2686,12 +2852,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Creative Newtech Limited</t>
+          <t>KRN Heat Exchanger and Refrigeration Limited</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2705,21 +2871,21 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1867</v>
+        <v>9611</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1226</v>
+        <v>1398.4</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1226</v>
+        <v>1398.4</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -2730,44 +2896,50 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>95.20999999999999</v>
+        <v>18.15</v>
       </c>
       <c r="N24" s="2" t="n">
+        <v>90.48999999999999</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>58.99</v>
+      </c>
+      <c r="P24" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n">
-        <v>91.3</v>
       </c>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="T24" s="2" t="n">
-        <v>70</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="T24" s="2" t="n"/>
       <c r="U24" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+        <v>97</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2779,12 +2951,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Standard Engineering Technology Limited</t>
+          <t>Ram Ratna Wires Limited</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2798,69 +2970,75 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>5953</v>
+        <v>4435</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>297.65</v>
+        <v>475.05</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>300.05</v>
+        <v>475.05</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>84.11</v>
+        <v>13</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.95</v>
+        <v>52.24</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P25" s="2" t="n"/>
+        <v>39.18</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>4.03</v>
+      </c>
       <c r="Q25" s="2" t="n">
-        <v>80.2</v>
+        <v>4.42</v>
       </c>
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="T25" s="2" t="n">
-        <v>83</v>
-      </c>
+        <v>35.1</v>
+      </c>
+      <c r="T25" s="2" t="n"/>
       <c r="U25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+        <v>128</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2872,12 +3050,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Shadowfax Technologies Limited</t>
+          <t>Avalon Technologies Limited</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2891,69 +3069,75 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>14742</v>
+        <v>12967</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>251.33</v>
+        <v>1940.8</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>251.33</v>
+        <v>1965.3</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>128.52</v>
+        <v>46.69</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.22</v>
+        <v>84.13</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="P26" s="2" t="n"/>
+        <v>131.67</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>4.03</v>
+      </c>
       <c r="Q26" s="2" t="n">
-        <v>126.3</v>
+        <v>4.42</v>
       </c>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="T26" s="2" t="n">
-        <v>112</v>
-      </c>
+        <v>127.6</v>
+      </c>
+      <c r="T26" s="2" t="n"/>
       <c r="U26" s="2" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+        <v>134</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2965,12 +3149,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>SENORES</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC Mechatronics Limited</t>
+          <t>Senores Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2984,69 +3168,75 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>13927</v>
+        <v>6805</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3152.9</v>
+        <v>1491.4</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3152.9</v>
+        <v>1492.4</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>117.28</v>
+        <v>56.22</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>7.04</v>
+        <v>85.73</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="P27" s="2" t="n"/>
+        <v>119.21</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>3.95</v>
+      </c>
       <c r="Q27" s="2" t="n">
-        <v>110.2</v>
+        <v>4.31</v>
       </c>
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="T27" s="2" t="n">
-        <v>104</v>
-      </c>
+        <v>115.3</v>
+      </c>
+      <c r="T27" s="2" t="n"/>
       <c r="U27" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
+        <v>131</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3058,12 +3248,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MBAPL</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Madhya Bharat Agro Products Limited</t>
+          <t>Creative Newtech Limited</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3077,21 +3267,21 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>7381</v>
+        <v>1867</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>168.12</v>
+        <v>1226</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>168.12</v>
+        <v>1226</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -3102,44 +3292,50 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>99.95</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="N28" s="2" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>95.20999999999999</v>
+      </c>
+      <c r="P28" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O28" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P28" s="2" t="n"/>
-      <c r="Q28" s="2" t="n">
-        <v>96</v>
       </c>
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="T28" s="2" t="n">
-        <v>150</v>
-      </c>
+        <v>91.3</v>
+      </c>
+      <c r="T28" s="2" t="n"/>
       <c r="U28" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3151,12 +3347,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Vadilal Industries Limited</t>
+          <t>Standard Engineering Technology Limited</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3170,69 +3366,75 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>5572</v>
+        <v>5953</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7781</v>
+        <v>297.65</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7781</v>
+        <v>300.05</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>56.81</v>
+        <v>121.63</v>
       </c>
       <c r="N29" s="2" t="n">
+        <v>123.46</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>84.11</v>
+      </c>
+      <c r="P29" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="Q29" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="n">
-        <v>52.9</v>
       </c>
       <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n">
-        <v>219</v>
-      </c>
-      <c r="T29" s="2" t="n">
-        <v>156</v>
-      </c>
+        <v>80.2</v>
+      </c>
+      <c r="T29" s="2" t="n"/>
       <c r="U29" s="2" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+        <v>88</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3244,12 +3446,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Kapston Services Limited</t>
+          <t>Shadowfax Technologies Limited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3263,69 +3465,75 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1791</v>
+        <v>14742</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>585.1</v>
+        <v>251.33</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>585.1</v>
+        <v>251.33</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>136.39</v>
+        <v>33.28</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>3.95</v>
+        <v>101.5</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P30" s="2" t="n"/>
+        <v>128.52</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>2.22</v>
+      </c>
       <c r="Q30" s="2" t="n">
-        <v>132.4</v>
+        <v>3.03</v>
       </c>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="T30" s="2" t="n">
-        <v>28.1</v>
-      </c>
+        <v>126.3</v>
+      </c>
+      <c r="T30" s="2" t="n"/>
       <c r="U30" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+        <v>169</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3337,40 +3545,40 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>SEDEMAC Mechatronics Limited</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>SME</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1399</v>
+        <v>13927</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>583</v>
+        <v>3152.9</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>583</v>
+        <v>3152.9</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -3381,48 +3589,48 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>100.58</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>4.03</v>
-      </c>
+        <v>59.08</v>
+      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n">
-        <v>4.42</v>
+        <v>117.28</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>-3.8</v>
+        <v>7.04</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>104.4</v>
-      </c>
+        <v>7.83</v>
+      </c>
+      <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="T31" s="2" t="n">
-        <v>44</v>
-      </c>
+        <v>110.2</v>
+      </c>
+      <c r="T31" s="2" t="n"/>
       <c r="U31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+        <v>106</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
       <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3434,12 +3642,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>KINGFA</t>
+          <t>MBAPL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kingfa Science &amp; Technology (India) Limited</t>
+          <t>Madhya Bharat Agro Products Limited</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3453,21 +3661,21 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7955</v>
+        <v>7381</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6028.5</v>
+        <v>168.12</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>6028.5</v>
+        <v>168.12</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -3478,44 +3686,50 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>67.20999999999999</v>
+        <v>58.62</v>
       </c>
       <c r="N32" s="2" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="P32" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O32" s="2" t="n">
+      <c r="Q32" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="n">
-        <v>63.3</v>
       </c>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="T32" s="2" t="n">
-        <v>185</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="T32" s="2" t="n"/>
       <c r="U32" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+        <v>155</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3527,12 +3741,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>KENNAMET</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Kennametal India Limited</t>
+          <t>Vadilal Industries Limited</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3546,21 +3760,21 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>7722</v>
+        <v>5572</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3674.1</v>
+        <v>7781</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3674.1</v>
+        <v>7781</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -3571,44 +3785,50 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>48.38</v>
+        <v>83.44</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>26.31</v>
+        <v>50.13</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="P33" s="2" t="n"/>
+        <v>56.81</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>3.95</v>
+      </c>
       <c r="Q33" s="2" t="n">
-        <v>22.1</v>
+        <v>4.31</v>
       </c>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="T33" s="2" t="n">
-        <v>114</v>
-      </c>
+        <v>52.9</v>
+      </c>
+      <c r="T33" s="2" t="n"/>
       <c r="U33" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+        <v>219</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t>Sep 2022</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3620,12 +3840,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>KSH International Limited</t>
+          <t>Kapston Services Limited</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3639,69 +3859,75 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>6969</v>
+        <v>1791</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1028.6</v>
+        <v>585.1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1028.6</v>
+        <v>585.1</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>189.75</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.26</v>
+        <v>48.82</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="P34" s="2" t="n"/>
+        <v>136.39</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>3.95</v>
+      </c>
       <c r="Q34" s="2" t="n">
-        <v>191</v>
+        <v>4.31</v>
       </c>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="T34" s="2" t="n">
-        <v>111</v>
-      </c>
+        <v>132.4</v>
+      </c>
+      <c r="T34" s="2" t="n"/>
       <c r="U34" s="2" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
+        <v>30.5</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3713,88 +3939,98 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>SG Mart Limited</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>9274</v>
+        <v>1399</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>747.15</v>
+        <v>583</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>747.15</v>
+        <v>583</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>108.64</v>
+        <v>32.12</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.74</v>
+        <v>81.14</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P35" s="2" t="n"/>
+        <v>100.58</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>4.03</v>
+      </c>
       <c r="Q35" s="2" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="R35" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="S35" s="2" t="n">
-        <v>125</v>
+        <v>96.5</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>120</v>
+        <v>104.4</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3806,12 +4042,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>COMSYN</t>
+          <t>KINGFA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Commercial Syn Bags Limited</t>
+          <t>Kingfa Science &amp; Technology (India) Limited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3825,21 +4061,21 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1163</v>
+        <v>7955</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>282.66</v>
+        <v>6028.5</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>282.66</v>
+        <v>6028.5</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -3850,44 +4086,50 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>108.34</v>
+        <v>16.48</v>
       </c>
       <c r="N36" s="2" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>67.20999999999999</v>
+      </c>
+      <c r="P36" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="Q36" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P36" s="2" t="n"/>
-      <c r="Q36" s="2" t="n">
-        <v>104.4</v>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="T36" s="2" t="n">
-        <v>28</v>
-      </c>
+        <v>63.3</v>
+      </c>
+      <c r="T36" s="2" t="n"/>
       <c r="U36" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
+        <v>225</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3899,12 +4141,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>KENNAMET</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited</t>
+          <t>Kennametal India Limited</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3914,77 +4156,79 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>16077</v>
+        <v>7722</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>807.05</v>
+        <v>3674.1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>819.7</v>
+        <v>3674.1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>78.12</v>
+        <v>22.41</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>3.95</v>
+        <v>48.38</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>4.31</v>
+        <v>48.38</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>12.35</v>
+        <v>26.31</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="R37" s="2" t="n">
-        <v>65.8</v>
-      </c>
+        <v>26.99</v>
+      </c>
+      <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="T37" s="2" t="n">
-        <v>244</v>
-      </c>
+        <v>22.1</v>
+      </c>
+      <c r="T37" s="2" t="n"/>
       <c r="U37" s="2" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
+        <v>118</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2022</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3996,12 +4240,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>KDDL</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>KDDL Limited</t>
+          <t>KSH International Limited</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4015,7 +4259,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4834</v>
+        <v>6969</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -4023,61 +4267,67 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3945.9</v>
+        <v>1028.6</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>3945.9</v>
+        <v>1028.6</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>56.61</v>
+        <v>61.92</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3.95</v>
+        <v>184.97</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P38" s="2" t="n"/>
+        <v>189.75</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>-1.26</v>
+      </c>
       <c r="Q38" s="2" t="n">
-        <v>52.7</v>
+        <v>-0.63</v>
       </c>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="T38" s="2" t="n">
-        <v>146</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="T38" s="2" t="n"/>
       <c r="U38" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
+        <v>130</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X38" s="2" t="inlineStr">
+      <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y38" s="2" t="inlineStr">
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4089,12 +4339,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Limited</t>
+          <t>SG Mart Limited</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4108,69 +4358,75 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>11430</v>
+        <v>9274</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2464.9</v>
+        <v>747.15</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2480.4</v>
+        <v>747.15</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>-0.62</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>97.41</v>
+        <v>23.9</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>3.95</v>
+        <v>75.7</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P39" s="2" t="n"/>
+        <v>108.64</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>1.74</v>
+      </c>
       <c r="Q39" s="2" t="n">
-        <v>93.5</v>
+        <v>2.1</v>
       </c>
       <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n">
-        <v>304</v>
-      </c>
-      <c r="T39" s="2" t="n">
-        <v>271</v>
-      </c>
+        <v>106.9</v>
+      </c>
+      <c r="T39" s="2" t="n"/>
       <c r="U39" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="Y39" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="Z39" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4182,12 +4438,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>COMSYN</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sudeep Pharma Limited</t>
+          <t>Commercial Syn Bags Limited</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4197,77 +4453,79 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nifty Chemicals</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>12487</v>
+        <v>1163</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1105.55</v>
+        <v>282.66</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1108.4</v>
+        <v>282.66</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>42.81</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.41</v>
+        <v>55.03</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>-0.85</v>
+        <v>108.34</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>6.68</v>
+        <v>3.95</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="R40" s="2" t="n">
-        <v>36.1</v>
-      </c>
+        <v>4.31</v>
+      </c>
+      <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="T40" s="2" t="n">
-        <v>175</v>
-      </c>
+        <v>104.4</v>
+      </c>
+      <c r="T40" s="2" t="n"/>
       <c r="U40" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
+        <v>29.7</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X40" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y40" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4279,12 +4537,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited</t>
+          <t>Shilpa Medicare Limited</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4294,73 +4552,83 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>19721</v>
+        <v>16077</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2007.6</v>
+        <v>807.05</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2022.7</v>
+        <v>819.7</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-0.75</v>
+        <v>-1.54</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>113.31</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="N41" s="2" t="n">
+        <v>149.74</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="P41" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O41" s="2" t="n">
+      <c r="Q41" s="2" t="n">
         <v>4.31</v>
       </c>
-      <c r="P41" s="2" t="n"/>
-      <c r="Q41" s="2" t="n">
-        <v>109.4</v>
-      </c>
-      <c r="R41" s="2" t="n"/>
+      <c r="R41" s="2" t="n">
+        <v>12.35</v>
+      </c>
       <c r="S41" s="2" t="n">
-        <v>327</v>
+        <v>74.2</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>302</v>
+        <v>65.8</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
+        <v>298</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr">
+      <c r="Y41" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X41" s="2" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4372,12 +4640,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>KDDL</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>KDDL Limited</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4391,21 +4659,21 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1382</v>
+        <v>4834</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>166.77</v>
+        <v>3945.9</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>166.77</v>
+        <v>3945.9</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -4416,44 +4684,50 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>47.54</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>11.16</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="P42" s="2" t="n"/>
+        <v>56.61</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>3.95</v>
+      </c>
       <c r="Q42" s="2" t="n">
-        <v>36.4</v>
+        <v>4.31</v>
       </c>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="T42" s="2" t="n">
-        <v>50</v>
-      </c>
+        <v>52.7</v>
+      </c>
+      <c r="T42" s="2" t="n"/>
       <c r="U42" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
+        <v>151</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
+      <c r="Z42" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4465,12 +4739,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>GSP Crop Science Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4484,69 +4758,73 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2774</v>
+        <v>2611</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>591.7</v>
+        <v>5403</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>597.5</v>
+        <v>5418</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>-0.97</v>
+        <v>-0.28</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>66.09</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>12</v>
-      </c>
+        <v>6.85</v>
+      </c>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="P43" s="2" t="n"/>
+        <v>12.85</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>3.19</v>
+      </c>
       <c r="Q43" s="2" t="n">
-        <v>54.1</v>
+        <v>3.72</v>
       </c>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="T43" s="2" t="n">
-        <v>97</v>
-      </c>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="T43" s="2" t="n"/>
       <c r="U43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X43" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y43" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4558,12 +4836,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Krishana Phoschem Limited</t>
+          <t>Pearl Global Industries Limited</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4577,69 +4855,75 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>5895</v>
+        <v>11430</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>188.94</v>
+        <v>2464.9</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>188.94</v>
+        <v>2480.4</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>75.34999999999999</v>
+        <v>61.23</v>
       </c>
       <c r="N44" s="2" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="P44" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O44" s="2" t="n">
+      <c r="Q44" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="n">
-        <v>71.40000000000001</v>
       </c>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="T44" s="2" t="n">
-        <v>180</v>
-      </c>
+        <v>93.5</v>
+      </c>
+      <c r="T44" s="2" t="n"/>
       <c r="U44" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
+        <v>304</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X44" s="2" t="inlineStr">
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y44" s="2" t="inlineStr">
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4651,12 +4935,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
+          <t>Sudeep Pharma Limited</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4666,73 +4950,83 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Chemicals</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>2611</v>
+        <v>12487</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>5403</v>
+        <v>1105.55</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5418</v>
+        <v>1108.4</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7.34</v>
+        <v>70.36</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.94</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="P45" s="2" t="n"/>
+        <v>42.81</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>-1.41</v>
+      </c>
       <c r="Q45" s="2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="R45" s="2" t="n"/>
+        <v>-0.85</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>6.68</v>
+      </c>
       <c r="S45" s="2" t="n">
-        <v>75</v>
+        <v>44.2</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>70</v>
+        <v>36.1</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
+        <v>185</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="W45" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X45" s="2" t="inlineStr">
+      <c r="Z45" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4744,12 +5038,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>NGLFINE</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>NGL Fine-Chem Limited</t>
+          <t>Happy Forgings Limited</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4763,76 +5057,577 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>2135</v>
+        <v>19721</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3435.5</v>
+        <v>2007.6</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>3457.8</v>
+        <v>2022.7</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.75</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>159.83</v>
+        <v>45.08</v>
       </c>
       <c r="N46" s="2" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>113.31</v>
+      </c>
+      <c r="P46" s="2" t="n">
         <v>3.95</v>
       </c>
-      <c r="O46" s="2" t="n">
+      <c r="Q46" s="2" t="n">
         <v>4.31</v>
-      </c>
-      <c r="P46" s="2" t="n"/>
-      <c r="Q46" s="2" t="n">
-        <v>155.9</v>
       </c>
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="T46" s="2" t="n"/>
+      <c r="U46" s="2" t="n">
+        <v>327</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="W46" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>RSL</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Rajputana Stainless Limited</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>1382</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>166.77</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>166.77</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="R47" s="2" t="n"/>
+      <c r="S47" s="2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="T47" s="2" t="n"/>
+      <c r="U47" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>GSPCROP</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>GSP Crop Science Limited</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>2774</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>591.7</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>597.5</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="R48" s="2" t="n"/>
+      <c r="S48" s="2" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="T48" s="2" t="n"/>
+      <c r="U48" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>AAYUSHBULL</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1908</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>1245.9</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>1247.65</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>KRISHANA</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Krishana Phoschem Limited</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>5895</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>188.94</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>188.94</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="R50" s="2" t="n"/>
+      <c r="S50" s="2" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="T50" s="2" t="n"/>
+      <c r="U50" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>NGL Fine-Chem Limited</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>2135</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>3435.5</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>3457.8</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>53.31</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>159.83</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="R51" s="2" t="n"/>
+      <c r="S51" s="2" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="T51" s="2" t="n"/>
+      <c r="U51" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="T46" s="2" t="n">
+      <c r="V51" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="U46" s="2" t="n">
+      <c r="W51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="X51" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="Y51" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
+      <c r="Z51" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
+      <c r="AA51" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y46"/>
+  <autoFilter ref="A1:AA51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4851,80 +5646,80 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ATH Radar - weekly screen</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr"/>
+      <c r="B1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Run date</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>2026-08-15 (prices as of 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Universe</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2126 NSE mainboard (EQ) + 547 NSE Emerge SME</t>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2126 NSE mainboard (EQ) + 1014 NSE Emerge SME</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Filters</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Within 2% of all-time-high close; TTM return above Nifty 500, Nifty Total Market, sector index (mainboard) / NIFTY SME EMERGE (SME); TTM PAT &gt;= every prior annual and rolling window (screener.in); mcap Rs 1,000-20,000 Cr</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Sort</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Newest entrant into the 2% ATH zone first; green rows new since previous run</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2673 screened -&gt; 148 at ATH -&gt; 140 outperforming -&gt; 90 record PAT -&gt; 45 in mcap band</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>3140 screened -&gt; 162 at ATH -&gt; 159 outperforming -&gt; 100 record PAT -&gt; 50 in mcap band</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Caveats</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>SME price history since Jul-2024, unadjusted for corporate actions; PAT history limited to screener-visible years; mainboard prices split-adjusted (Yahoo). Factual screen - not investment advice</t>
         </is>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -733,26 +733,26 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>KESAR</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>KESAR INDIA LIMITED</t>
+          <t>S.J.S. Enterprises Limited</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3956</v>
+        <v>8111</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -763,27 +763,27 @@
         <v>1</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1266.1</v>
+        <v>2532.5</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1284.85</v>
+        <v>2532.5</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>-1.46</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.83</v>
+        <v>33.1</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>14.27</v>
+        <v>40.41</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>94.78</v>
+        <v>115.28</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>4.03</v>
@@ -791,23 +791,19 @@
       <c r="Q3" s="3" t="n">
         <v>4.42</v>
       </c>
-      <c r="R3" s="3" t="n">
-        <v>-3.8</v>
-      </c>
+      <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
+        <v>111.2</v>
+      </c>
+      <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>51.6</v>
+        <v>22.7</v>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
@@ -831,204 +827,208 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>AFCOM</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Afcom Holdings Limited</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KESAR</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>KESAR INDIA LIMITED</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>SME-BSE</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>4311</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="n">
+        <v>3956</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>1502.05</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>1502.05</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>65.04000000000001</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="I4" s="2" t="n">
+        <v>1266.1</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1284.85</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>94.78</v>
+      </c>
+      <c r="P4" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="S4" s="2" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MANINDS</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Man Industries (India) Limited</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Pricol Limited</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4496</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Auto</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>9654</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>599.45</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>601.4</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="P5" s="2" t="n">
+      <c r="I5" s="3" t="n">
+        <v>792.05</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>792.05</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" s="3" t="n">
         <v>4.42</v>
       </c>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="W5" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="R5" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1038,26 +1038,26 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>KHAZANCHI</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Khazanchi Jewellers Limited</t>
+          <t>Rossell Techsys Limited</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1961</v>
+        <v>4047</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -1068,27 +1068,27 @@
         <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>792.45</v>
+        <v>1073.45</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>792.45</v>
+        <v>1094.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>-1.92</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>27.95</v>
+        <v>21</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>2.32</v>
+        <v>50.21</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>31.69</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>4.03</v>
@@ -1096,27 +1096,23 @@
       <c r="Q6" s="3" t="n">
         <v>4.42</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>-3.8</v>
-      </c>
+      <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>35.5</v>
-      </c>
+        <v>71.7</v>
+      </c>
+      <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n">
-        <v>103</v>
+        <v>25.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>14.4</v>
+        <v>16.8</v>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1141,26 +1137,26 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>AFCOM</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Manorama Industries Limited</t>
+          <t>Afcom Holdings Limited</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Nifty FMCG</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>10965</v>
+        <v>4311</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1171,10 +1167,10 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1737.1</v>
+        <v>1502.05</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1737.1</v>
+        <v>1502.05</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>33.05</v>
+        <v>66.34</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>23.17</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>26.21</v>
+        <v>68.75</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>4.03</v>
@@ -1200,26 +1196,26 @@
         <v>4.42</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-11.05</v>
+        <v>-3.8</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>22.2</v>
+        <v>64.7</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>37.3</v>
+        <v>72.5</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>258</v>
+        <v>146</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1244,12 +1240,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KMEW</t>
+          <t>MANINDS</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Knowledge Marine &amp; Engineering Works Limited</t>
+          <t>Man Industries (India) Limited</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1263,38 +1259,38 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6926</v>
+        <v>4496</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2730.8</v>
+        <v>599.45</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2730.8</v>
+        <v>601.4</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>38.07</v>
+        <v>7.02</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>60.83</v>
+        <v>41.33</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>227.22</v>
+        <v>51.22</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>4.03</v>
@@ -1304,17 +1300,17 @@
       </c>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n">
-        <v>223.2</v>
+        <v>47.2</v>
       </c>
       <c r="T8" s="2" t="n"/>
       <c r="U8" s="2" t="n">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>65</v>
+        <v>8.5</v>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
@@ -1338,101 +1334,105 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>RPEL</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Raghav Productivity Enhancers Limited</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>CORONA</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>CORONA Remedies Limited</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>6585</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>13071</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>1388.8</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>1388.8</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>85.23999999999999</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>130.81</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="T9" s="2" t="n"/>
-      <c r="U9" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="I9" s="3" t="n">
+        <v>2137.1</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>2159.7</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1442,81 +1442,85 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>KHAZANCHI</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Marine Electricals (India) Limited</t>
+          <t>Khazanchi Jewellers Limited</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5188</v>
+        <v>1961</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>371.2</v>
+        <v>792.45</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>371.2</v>
+        <v>792.45</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>69.7</v>
+        <v>27.95</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>97.23</v>
+        <v>2.32</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>116.08</v>
+        <v>31.69</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="R10" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="S10" s="2" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="T10" s="2" t="n"/>
+        <v>27.7</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>35.5</v>
+      </c>
       <c r="U10" s="2" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1541,12 +1545,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>STYLAMIND</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Stylam Industries Limited</t>
+          <t>Manorama Industries Limited</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1556,62 +1560,66 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty FMCG</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>6172</v>
+        <v>10965</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3595.7</v>
+        <v>1737.1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3651.2</v>
+        <v>1737.1</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-1.52</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>41.17</v>
+        <v>33.05</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>62.95</v>
+        <v>23.17</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>115.13</v>
+        <v>26.21</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="R11" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>-11.05</v>
+      </c>
       <c r="S11" s="2" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="T11" s="2" t="n"/>
+        <v>22.2</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>37.3</v>
+      </c>
       <c r="U11" s="2" t="n">
-        <v>169</v>
+        <v>258</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>12.7</v>
+        <v>14.2</v>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
@@ -1640,12 +1648,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>KMEW</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Azad Engineering Limited</t>
+          <t>Knowledge Marine &amp; Engineering Works Limited</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1659,7 +1667,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>17552</v>
+        <v>6926</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1667,50 +1675,50 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2665.1</v>
+        <v>2730.8</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2665.1</v>
+        <v>2730.8</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>22.11</v>
+        <v>38.07</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>65.45</v>
+        <v>60.83</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>75.48999999999999</v>
+        <v>227.22</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n">
-        <v>71.5</v>
+        <v>223.2</v>
       </c>
       <c r="T12" s="2" t="n"/>
       <c r="U12" s="2" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>4.5</v>
+        <v>65</v>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
@@ -1739,12 +1747,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>STEELCAS</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Steelcast Limited</t>
+          <t>Raghav Productivity Enhancers Limited</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1758,7 +1766,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3561</v>
+        <v>6585</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1766,54 +1774,54 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>354.15</v>
+        <v>1433.9</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>354.15</v>
+        <v>1433.9</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>23.61</v>
+        <v>73.7</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>54.55</v>
+        <v>94.84</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>71.09</v>
+        <v>137.2</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>133.2</v>
       </c>
       <c r="T13" s="2" t="n"/>
       <c r="U13" s="2" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -1833,105 +1841,101 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>CFF</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>CFF FLUID CONTROL LIMITED</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>2142</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>MARINE</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Marine Electricals (India) Limited</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5188</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>1021.35</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>1023.7</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>35.95</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>92.91</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>63.94</v>
-      </c>
-      <c r="P14" s="3" t="n">
+      <c r="I14" s="2" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>69.45999999999999</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>102.89</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>123.57</v>
+      </c>
+      <c r="P14" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1945,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>STYLAMIND</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>GHCL Textiles Limited</t>
+          <t>Stylam Industries Limited</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1960,7 +1964,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1129</v>
+        <v>6172</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1968,54 +1972,54 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>121.26</v>
+        <v>3642</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>121.59</v>
+        <v>3651.2</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>35.53</v>
+        <v>37.24</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>57.26</v>
+        <v>64.17</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>55.52</v>
+        <v>119.28</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n">
-        <v>51.6</v>
+        <v>115.2</v>
       </c>
       <c r="T15" s="2" t="n"/>
       <c r="U15" s="2" t="n">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>35.2</v>
+        <v>12.7</v>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2040,12 +2044,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences Limited</t>
+          <t>Azad Engineering Limited</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2055,11 +2059,11 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>17025</v>
+        <v>17552</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -2067,58 +2071,54 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1374.6</v>
+        <v>2717.8</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1393.6</v>
+        <v>2717.8</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-1.36</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>29.18</v>
+        <v>29.53</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>48.98</v>
+        <v>72.11</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>43.43</v>
+        <v>75.25</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>12.35</v>
-      </c>
+        <v>4.42</v>
+      </c>
+      <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>31.1</v>
-      </c>
+        <v>71.2</v>
+      </c>
+      <c r="T16" s="2" t="n"/>
       <c r="U16" s="2" t="n">
-        <v>603</v>
+        <v>140</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>565</v>
+        <v>134</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>JGCHEM</t>
+          <t>STEELCAS</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>J.G.Chemicals Limited</t>
+          <t>Steelcast Limited</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2375</v>
+        <v>3561</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -2170,54 +2170,54 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>613</v>
+        <v>351.85</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>622.35</v>
+        <v>354.15</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-1.5</v>
+        <v>-0.65</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>47.3</v>
+        <v>24.28</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>52.96</v>
+        <v>56.9</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>25.68</v>
+        <v>69.08</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n">
-        <v>21.7</v>
+        <v>65</v>
       </c>
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2242,26 +2242,26 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>CFF</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
+          <t>CFF FLUID CONTROL LIMITED</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>17034</v>
+        <v>2142</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -2269,64 +2269,68 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>508.45</v>
+        <v>1021.35</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>518</v>
+        <v>1023.7</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-1.84</v>
+        <v>-0.23</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>24.03</v>
+        <v>35.95</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>13.67</v>
+        <v>92.91</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>16.24</v>
+        <v>63.94</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="R18" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="S18" s="2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="T18" s="2" t="n"/>
+        <v>59.9</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>67.7</v>
+      </c>
       <c r="U18" s="2" t="n">
-        <v>444</v>
+        <v>39</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>404</v>
+        <v>39</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2341,57 +2345,57 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>Alivus Life Sciences Limited</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2202</v>
+        <v>17025</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>852</v>
+        <v>1386.7</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>852</v>
+        <v>1393.6</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>126.75</v>
+        <v>32.75</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>182.07</v>
+        <v>50.76</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>176.04</v>
+        <v>46.88</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>4.03</v>
@@ -2400,22 +2404,22 @@
         <v>4.42</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>-3.8</v>
+        <v>12.7</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>172</v>
+        <v>42.9</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>179.8</v>
+        <v>34.2</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>31.5</v>
+        <v>603</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>27</v>
+        <v>565</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
@@ -2444,57 +2448,57 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2065</v>
+        <v>17034</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>950.25</v>
+        <v>510.05</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>967.6</v>
+        <v>518</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-1.79</v>
+        <v>-1.53</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>81.73</v>
+        <v>23.16</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>105.55</v>
+        <v>14.55</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>137.56</v>
+        <v>16.13</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>4.03</v>
@@ -2502,23 +2506,19 @@
       <c r="Q20" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R20" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="T20" s="2" t="n">
-        <v>141.4</v>
-      </c>
+        <v>12.1</v>
+      </c>
+      <c r="T20" s="2" t="n"/>
       <c r="U20" s="2" t="n">
-        <v>29</v>
+        <v>444</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>23</v>
+        <v>404</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>26.1</v>
+        <v>9.9</v>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
@@ -2547,26 +2547,26 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>DIVGIITTS</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Divgi Torqtransfer Systems Limited</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>3979</v>
+        <v>2202</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -2577,10 +2577,10 @@
         <v>3</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1301.05</v>
+        <v>852</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1301.05</v>
+        <v>852</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>95.94</v>
+        <v>126.75</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>74.73999999999999</v>
+        <v>182.07</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>101.34</v>
+        <v>176.04</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>4.03</v>
@@ -2605,19 +2605,23 @@
       <c r="Q21" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R21" s="2" t="n"/>
+      <c r="R21" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="S21" s="2" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="T21" s="2" t="n"/>
+        <v>172</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>179.8</v>
+      </c>
       <c r="U21" s="2" t="n">
-        <v>63</v>
+        <v>31.5</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>23.5</v>
+        <v>16.7</v>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
@@ -2646,26 +2650,26 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>MONOLITH</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SPR Auto Technologies Limited</t>
+          <t>MONOLITH</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Nifty Auto</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>19789</v>
+        <v>2065</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -2673,54 +2677,54 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4487.7</v>
+        <v>950.25</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>4524.4</v>
+        <v>967.6</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.79</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>34.07</v>
+        <v>81.73</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>42.2</v>
+        <v>105.55</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>83.5</v>
+        <v>137.56</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>21.08</v>
+        <v>-3.8</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>79.5</v>
+        <v>133.5</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>62.4</v>
+        <v>141.4</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>575</v>
+        <v>29</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>562</v>
+        <v>23</v>
       </c>
       <c r="W22" s="2" t="n">
-        <v>2.3</v>
+        <v>26.1</v>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
@@ -2749,12 +2753,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>DIVGIITTS</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>The Karnataka Bank Limited</t>
+          <t>Divgi Torqtransfer Systems Limited</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2764,11 +2768,11 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Nifty Financial Services</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>11714</v>
+        <v>3979</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -2779,27 +2783,27 @@
         <v>3</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>309.65</v>
+        <v>1301.05</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>313.7</v>
+        <v>1301.05</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-1.29</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>25.82</v>
+        <v>95.94</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>52.75</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>82.26000000000001</v>
+        <v>101.34</v>
       </c>
       <c r="P23" s="2" t="n">
         <v>4.03</v>
@@ -2807,27 +2811,23 @@
       <c r="Q23" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R23" s="2" t="n">
-        <v>-0.45</v>
-      </c>
+      <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="T23" s="2" t="n">
-        <v>82.7</v>
-      </c>
+        <v>97.3</v>
+      </c>
+      <c r="T23" s="2" t="n"/>
       <c r="U23" s="2" t="n">
-        <v>1437</v>
+        <v>63</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>1341</v>
+        <v>51</v>
       </c>
       <c r="W23" s="2" t="n">
-        <v>7.2</v>
+        <v>23.5</v>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>KRN Heat Exchanger and Refrigeration Limited</t>
+          <t>SPR Auto Technologies Limited</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2867,11 +2867,11 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Auto</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>9611</v>
+        <v>19789</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -2879,50 +2879,54 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1398.4</v>
+        <v>4492.4</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1398.4</v>
+        <v>4524.4</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>18.15</v>
+        <v>32.69</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>90.48999999999999</v>
+        <v>45.67</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>58.99</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="R24" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>21.1</v>
+      </c>
       <c r="S24" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="T24" s="2" t="n"/>
+        <v>78.59999999999999</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>61.6</v>
+      </c>
       <c r="U24" s="2" t="n">
-        <v>97</v>
+        <v>575</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>76</v>
+        <v>562</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>27.6</v>
+        <v>2.3</v>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
@@ -2951,12 +2955,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Ram Ratna Wires Limited</t>
+          <t>The Karnataka Bank Limited</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2966,11 +2970,11 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Financial Services</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>4435</v>
+        <v>11714</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -2981,27 +2985,27 @@
         <v>3</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>475.05</v>
+        <v>309.65</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>475.05</v>
+        <v>313.7</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>-1.29</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>13</v>
+        <v>25.82</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>52.24</v>
+        <v>52.75</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>39.18</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>4.03</v>
@@ -3009,19 +3013,23 @@
       <c r="Q25" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R25" s="2" t="n"/>
+      <c r="R25" s="2" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="S25" s="2" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="T25" s="2" t="n"/>
+        <v>78.2</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>82.7</v>
+      </c>
       <c r="U25" s="2" t="n">
-        <v>128</v>
+        <v>1437</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>109</v>
+        <v>1341</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>17.4</v>
+        <v>7.2</v>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
@@ -3050,12 +3058,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>KRN Heat Exchanger and Refrigeration Limited</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3069,38 +3077,38 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>12967</v>
+        <v>9611</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1940.8</v>
+        <v>1468.3</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1965.3</v>
+        <v>1468.3</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>46.69</v>
+        <v>25.22</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>84.13</v>
+        <v>105.3</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>131.67</v>
+        <v>72.13</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>4.03</v>
@@ -3110,17 +3118,17 @@
       </c>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n">
-        <v>127.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="T26" s="2" t="n"/>
       <c r="U26" s="2" t="n">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>18.6</v>
+        <v>27.6</v>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
@@ -3149,12 +3157,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SENORES</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Senores Pharmaceuticals Limited</t>
+          <t>Ram Ratna Wires Limited</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3168,58 +3176,58 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>6805</v>
+        <v>4435</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1491.4</v>
+        <v>475.05</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1492.4</v>
+        <v>475.05</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>56.22</v>
+        <v>13</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>85.73</v>
+        <v>52.24</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>119.21</v>
+        <v>39.18</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n">
-        <v>115.3</v>
+        <v>35.1</v>
       </c>
       <c r="T27" s="2" t="n"/>
       <c r="U27" s="2" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>7.4</v>
+        <v>17.4</v>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
@@ -3248,12 +3256,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Creative Newtech Limited</t>
+          <t>Avalon Technologies Limited</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3267,7 +3275,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1867</v>
+        <v>12967</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -3275,50 +3283,50 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1226</v>
+        <v>1940.8</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1226</v>
+        <v>1965.3</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>82.93000000000001</v>
+        <v>46.69</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>87.43000000000001</v>
+        <v>84.13</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>95.20999999999999</v>
+        <v>131.67</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n">
-        <v>91.3</v>
+        <v>127.6</v>
       </c>
       <c r="T28" s="2" t="n"/>
       <c r="U28" s="2" t="n">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>5.7</v>
+        <v>18.6</v>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
@@ -3347,12 +3355,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>SENORES</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Standard Engineering Technology Limited</t>
+          <t>Senores Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3366,7 +3374,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>5953</v>
+        <v>6805</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -3374,16 +3382,16 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>297.65</v>
+        <v>1477.7</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>300.05</v>
+        <v>1492.4</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.98</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -3391,33 +3399,33 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>121.63</v>
+        <v>40.69</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>123.46</v>
+        <v>88.59</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>84.11</v>
+        <v>118.84</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n">
-        <v>80.2</v>
+        <v>114.8</v>
       </c>
       <c r="T29" s="2" t="n"/>
       <c r="U29" s="2" t="n">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="W29" s="2" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
@@ -3446,12 +3454,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Shadowfax Technologies Limited</t>
+          <t>Creative Newtech Limited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3465,21 +3473,21 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>14742</v>
+        <v>1867</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>251.33</v>
+        <v>1243</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>251.33</v>
+        <v>1243</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -3490,33 +3498,33 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>33.28</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>101.5</v>
+        <v>89.94</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>128.52</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>2.22</v>
+        <v>4.03</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>3.03</v>
+        <v>4.42</v>
       </c>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n">
-        <v>126.3</v>
+        <v>95.7</v>
       </c>
       <c r="T30" s="2" t="n"/>
       <c r="U30" s="2" t="n">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="W30" s="2" t="n">
-        <v>50.9</v>
+        <v>5.7</v>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
@@ -3545,12 +3553,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC Mechatronics Limited</t>
+          <t>Standard Engineering Technology Limited</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3564,60 +3572,62 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>13927</v>
+        <v>5953</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3152.9</v>
+        <v>298.4</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3152.9</v>
+        <v>300.05</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="N31" s="2" t="n"/>
+        <v>118.88</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>127.08</v>
+      </c>
       <c r="O31" s="2" t="n">
-        <v>117.28</v>
+        <v>84.17</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>7.04</v>
+        <v>4.03</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>7.83</v>
+        <v>4.42</v>
       </c>
       <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n">
-        <v>110.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="T31" s="2" t="n"/>
       <c r="U31" s="2" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="W31" s="2" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -3642,12 +3652,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MBAPL</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Madhya Bharat Agro Products Limited</t>
+          <t>Shadowfax Technologies Limited</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3661,7 +3671,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7381</v>
+        <v>14742</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -3669,54 +3679,54 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>168.12</v>
+        <v>251.33</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>168.12</v>
+        <v>251.33</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>58.62</v>
+        <v>33.28</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>79.63</v>
+        <v>101.5</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>99.95</v>
+        <v>128.52</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>3.95</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>4.31</v>
+        <v>3.03</v>
       </c>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n">
-        <v>96</v>
+        <v>126.3</v>
       </c>
       <c r="T32" s="2" t="n"/>
       <c r="U32" s="2" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="W32" s="2" t="n">
-        <v>3.3</v>
+        <v>50.9</v>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -3741,12 +3751,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>SEDEMAC</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Vadilal Industries Limited</t>
+          <t>SEDEMAC Mechatronics Limited</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3760,7 +3770,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>5572</v>
+        <v>13927</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -3768,54 +3778,52 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7781</v>
+        <v>3152.9</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7781</v>
+        <v>3152.9</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>50.13</v>
-      </c>
+        <v>59.08</v>
+      </c>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n">
-        <v>56.81</v>
+        <v>117.28</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>3.95</v>
+        <v>7.04</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>4.31</v>
+        <v>7.83</v>
       </c>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n">
-        <v>52.9</v>
+        <v>110.2</v>
       </c>
       <c r="T33" s="2" t="n"/>
       <c r="U33" s="2" t="n">
-        <v>219</v>
+        <v>106</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="W33" s="2" t="n">
-        <v>40.4</v>
+        <v>1.9</v>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -3840,12 +3848,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>MBAPL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kapston Services Limited</t>
+          <t>Madhya Bharat Agro Products Limited</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3859,62 +3867,62 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1791</v>
+        <v>7381</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>585.1</v>
+        <v>168.46</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>585.1</v>
+        <v>168.46</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>74.01000000000001</v>
+        <v>57.35</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>48.82</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>136.39</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n">
-        <v>132.4</v>
+        <v>95.5</v>
       </c>
       <c r="T34" s="2" t="n"/>
       <c r="U34" s="2" t="n">
-        <v>30.5</v>
+        <v>155</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>28.1</v>
+        <v>150</v>
       </c>
       <c r="W34" s="2" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -3939,57 +3947,57 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>Vadilal Industries Limited</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1399</v>
+        <v>5572</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>583</v>
+        <v>7749</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>583</v>
+        <v>7781</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>32.12</v>
+        <v>84.89</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>81.14</v>
+        <v>50.78</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>100.58</v>
+        <v>58.01</v>
       </c>
       <c r="P35" s="2" t="n">
         <v>4.03</v>
@@ -3997,37 +4005,33 @@
       <c r="Q35" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R35" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+      <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>104.4</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="T35" s="2" t="n"/>
       <c r="U35" s="2" t="n">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>44</v>
+        <v>156</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>0</v>
+        <v>40.4</v>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4042,12 +4046,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KINGFA</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Kingfa Science &amp; Technology (India) Limited</t>
+          <t>Kapston Services Limited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4061,7 +4065,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>7955</v>
+        <v>1791</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -4069,54 +4073,54 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6028.5</v>
+        <v>588.4</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6028.5</v>
+        <v>588.4</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>16.48</v>
+        <v>79.5</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>37.81</v>
+        <v>49</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>67.20999999999999</v>
+        <v>140.29</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n">
-        <v>63.3</v>
+        <v>136.3</v>
       </c>
       <c r="T36" s="2" t="n"/>
       <c r="U36" s="2" t="n">
-        <v>225</v>
+        <v>30.5</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>185</v>
+        <v>28.1</v>
       </c>
       <c r="W36" s="2" t="n">
-        <v>21.6</v>
+        <v>8.5</v>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4141,91 +4145,95 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>KENNAMET</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Kennametal India Limited</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>7722</v>
+        <v>1399</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3674.1</v>
+        <v>583</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3674.1</v>
+        <v>583</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>22.41</v>
+        <v>32.12</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>48.38</v>
+        <v>81.14</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>48.38</v>
+        <v>100.58</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>26.31</v>
+        <v>4.03</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>26.99</v>
-      </c>
-      <c r="R37" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="S37" s="2" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="T37" s="2" t="n"/>
+        <v>96.5</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>104.4</v>
+      </c>
       <c r="U37" s="2" t="n">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4366,16 +4374,16 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>747.15</v>
+        <v>735.85</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>747.15</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>-1.51</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -4383,13 +4391,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>23.9</v>
+        <v>22.8</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>75.7</v>
+        <v>75.66</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>108.64</v>
+        <v>105.49</v>
       </c>
       <c r="P39" s="2" t="n">
         <v>1.74</v>
@@ -4399,7 +4407,7 @@
       </c>
       <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n">
-        <v>106.9</v>
+        <v>103.8</v>
       </c>
       <c r="T39" s="2" t="n"/>
       <c r="U39" s="2" t="n">
@@ -4465,40 +4473,40 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>282.66</v>
+        <v>288.33</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>282.66</v>
+        <v>288.33</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>84.65000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>55.03</v>
+        <v>58.46</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>108.34</v>
+        <v>103.74</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n">
-        <v>104.4</v>
+        <v>99.7</v>
       </c>
       <c r="T40" s="2" t="n"/>
       <c r="U40" s="2" t="n">
@@ -4564,45 +4572,45 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>807.05</v>
+        <v>822</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>819.7</v>
+        <v>822</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>79.15000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>149.74</v>
+        <v>151.53</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>78.12</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>12.35</v>
+        <v>12.7</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>74.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>65.8</v>
+        <v>68.2</v>
       </c>
       <c r="U41" s="2" t="n">
         <v>298</v>
@@ -4667,16 +4675,16 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3945.9</v>
+        <v>3930.2</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>3945.9</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -4684,23 +4692,23 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>73.31999999999999</v>
+        <v>74.91</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>65.51000000000001</v>
+        <v>70.94</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>56.61</v>
+        <v>51.66</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n">
-        <v>52.7</v>
+        <v>47.6</v>
       </c>
       <c r="T42" s="2" t="n"/>
       <c r="U42" s="2" t="n">
@@ -4739,12 +4747,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
+          <t>Pearl Global Industries Limited</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4758,60 +4766,62 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2611</v>
+        <v>11430</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>5403</v>
+        <v>2474.6</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5418</v>
+        <v>2480.4</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.23</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="N43" s="2" t="n"/>
+        <v>48.04</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>56.02</v>
+      </c>
       <c r="O43" s="2" t="n">
-        <v>12.85</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>3.19</v>
+        <v>4.03</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>3.72</v>
+        <v>4.42</v>
       </c>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T43" s="2" t="n"/>
       <c r="U43" s="2" t="n">
-        <v>75</v>
+        <v>304</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>70</v>
+        <v>271</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>7.1</v>
+        <v>12.2</v>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -4836,12 +4846,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Limited</t>
+          <t>Sudeep Pharma Limited</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4851,11 +4861,11 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Chemicals</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>11430</v>
+        <v>12487</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -4863,50 +4873,54 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2464.9</v>
+        <v>1105.55</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2480.4</v>
+        <v>1108.4</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.26</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>61.23</v>
+        <v>70.36</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>55.03</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>97.41</v>
+        <v>42.81</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>3.95</v>
+        <v>-1.41</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="R44" s="2" t="n"/>
+        <v>-0.85</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>6.68</v>
+      </c>
       <c r="S44" s="2" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="T44" s="2" t="n"/>
+        <v>44.2</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>36.1</v>
+      </c>
       <c r="U44" s="2" t="n">
-        <v>304</v>
+        <v>185</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>271</v>
+        <v>175</v>
       </c>
       <c r="W44" s="2" t="n">
-        <v>12.2</v>
+        <v>5.7</v>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
@@ -4935,12 +4949,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Sudeep Pharma Limited</t>
+          <t>Happy Forgings Limited</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4950,66 +4964,62 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Nifty Chemicals</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>12487</v>
+        <v>19721</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1105.55</v>
+        <v>2089.6</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1108.4</v>
+        <v>2089.6</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>70.36</v>
+        <v>50.7</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>60.76</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>42.81</v>
+        <v>120.9</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>-1.41</v>
+        <v>4.03</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>6.68</v>
-      </c>
+        <v>4.42</v>
+      </c>
+      <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="T45" s="2" t="n">
-        <v>36.1</v>
-      </c>
+        <v>116.9</v>
+      </c>
+      <c r="T45" s="2" t="n"/>
       <c r="U45" s="2" t="n">
-        <v>185</v>
+        <v>327</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>175</v>
+        <v>302</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>5.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
@@ -5038,12 +5048,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited</t>
+          <t>Rajputana Stainless Limited</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5057,62 +5067,60 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>19721</v>
+        <v>1382</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2007.6</v>
+        <v>165.42</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2022.7</v>
+        <v>166.77</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>-0.75</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>56.04</v>
-      </c>
+        <v>19.29</v>
+      </c>
+      <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="n">
-        <v>113.31</v>
+        <v>46.35</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>3.95</v>
+        <v>11.16</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>4.31</v>
+        <v>11.94</v>
       </c>
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n">
-        <v>109.4</v>
+        <v>35.2</v>
       </c>
       <c r="T46" s="2" t="n"/>
       <c r="U46" s="2" t="n">
-        <v>327</v>
+        <v>58</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>302</v>
+        <v>50</v>
       </c>
       <c r="W46" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>16</v>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5137,12 +5145,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>GSP Crop Science Limited</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5156,60 +5164,60 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>1382</v>
+        <v>2774</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>166.77</v>
+        <v>596.25</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>166.77</v>
+        <v>597.5</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>22.63</v>
+        <v>39.38</v>
       </c>
       <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n">
-        <v>47.54</v>
+        <v>67.37</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>11.16</v>
+        <v>12</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>11.94</v>
+        <v>12.8</v>
       </c>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n">
-        <v>36.4</v>
+        <v>55.4</v>
       </c>
       <c r="T47" s="2" t="n"/>
       <c r="U47" s="2" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="W47" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -5234,89 +5242,95 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>AAYUSHBULL</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>GSP Crop Science Limited</t>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2774</v>
+        <v>1908</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>591.7</v>
+        <v>1245.9</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>597.5</v>
+        <v>1247.65</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>-0.97</v>
+        <v>-0.14</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>36.51</v>
-      </c>
-      <c r="N48" s="2" t="n"/>
+        <v>8.68</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>12.25</v>
+      </c>
       <c r="O48" s="2" t="n">
-        <v>66.09</v>
+        <v>32.63</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>12</v>
+        <v>4.03</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="R48" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="S48" s="2" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="T48" s="2" t="n"/>
+        <v>28.6</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>36.4</v>
+      </c>
       <c r="U48" s="2" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="W48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -5326,105 +5340,101 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>AAYUSHBULL</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>AAYUSH ART AND BULLION LIMITED</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>1908</v>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="n">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KRISHANA</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Krishana Phoschem Limited</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>5895</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="I49" s="3" t="n">
-        <v>1245.9</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>1247.65</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="N49" s="3" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="O49" s="3" t="n">
-        <v>32.63</v>
-      </c>
-      <c r="P49" s="3" t="n">
+      <c r="I49" s="2" t="n">
+        <v>190.68</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>190.68</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>86.03</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>75.11</v>
+      </c>
+      <c r="P49" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q49" s="3" t="n">
+      <c r="Q49" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R49" s="3" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="S49" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="T49" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="U49" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V49" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="W49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3" t="inlineStr">
+      <c r="R49" s="2" t="n"/>
+      <c r="S49" s="2" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="T49" s="2" t="n"/>
+      <c r="U49" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="Z49" s="3" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AA49" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5434,12 +5444,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Krishana Phoschem Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -5453,58 +5463,54 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>5895</v>
+        <v>2611</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>188.94</v>
+        <v>5403</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>188.94</v>
+        <v>5418</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>78.98999999999999</v>
-      </c>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n">
-        <v>75.34999999999999</v>
+        <v>7.34</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>3.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>4.31</v>
+        <v>2.06</v>
       </c>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="T50" s="2" t="n"/>
       <c r="U50" s="2" t="n">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="V50" s="2" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="W50" s="2" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
@@ -5560,16 +5566,16 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3435.5</v>
+        <v>3454</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>3457.8</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.11</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -5577,23 +5583,23 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>51.23</v>
+        <v>46.95</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>53.31</v>
+        <v>51.66</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>159.83</v>
+        <v>151.53</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>4.31</v>
+        <v>4.42</v>
       </c>
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n">
-        <v>155.9</v>
+        <v>147.5</v>
       </c>
       <c r="T51" s="2" t="n"/>
       <c r="U51" s="2" t="n">
@@ -5709,7 +5715,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3140 screened -&gt; 162 at ATH -&gt; 159 outperforming -&gt; 100 record PAT -&gt; 50 in mcap band</t>
+          <t>3140 screened -&gt; 173 at ATH -&gt; 166 outperforming -&gt; 99 record PAT -&gt; 50 in mcap band</t>
         </is>
       </c>
     </row>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,13 +74,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -728,101 +722,101 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>SJS</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>S.J.S. Enterprises Limited</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="2" t="n">
         <v>8111</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="2" t="n">
         <v>2532.5</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="2" t="n">
         <v>2532.5</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="2" t="n">
         <v>33.1</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="2" t="n">
         <v>40.41</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" s="2" t="n">
         <v>115.28</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="n">
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n">
         <v>111.2</v>
       </c>
-      <c r="T3" s="3" t="n"/>
-      <c r="U3" s="3" t="n">
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n">
         <v>211</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="W3" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -930,204 +924,204 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>PRICOLLTD</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Pricol Limited</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Nifty Auto</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="2" t="n">
         <v>9654</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="2" t="n">
         <v>792.05</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="2" t="n">
         <v>792.05</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="2" t="n">
         <v>28.85</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="2" t="n">
         <v>25.04</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O5" s="2" t="n">
         <v>85.04000000000001</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="P5" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="T5" s="3" t="n">
+      <c r="T5" s="2" t="n">
         <v>63.9</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" s="2" t="n">
         <v>268</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="2" t="n">
         <v>251</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>ROSSTECH</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Rossell Techsys Limited</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="2" t="n">
         <v>4047</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="2" t="n">
         <v>1073.45</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="2" t="n">
         <v>1094.5</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>-1.92</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="2" t="n">
         <v>50.21</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="2" t="n">
         <v>75.76000000000001</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n">
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n">
         <v>71.7</v>
       </c>
-      <c r="T6" s="3" t="n"/>
-      <c r="U6" s="3" t="n">
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="n">
         <v>25.7</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1334,105 +1328,105 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>CORONA</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>CORONA Remedies Limited</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Nifty Healthcare Index</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="2" t="n">
         <v>13071</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="2" t="n">
         <v>2137.1</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="2" t="n">
         <v>2159.7</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="2" t="n">
         <v>-1.05</v>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="2" t="n">
         <v>20.24</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="N9" s="2" t="n">
         <v>34.15</v>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="O9" s="2" t="n">
         <v>48.57</v>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.55</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="2" t="n">
         <v>0.09</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="2" t="n">
         <v>12.2</v>
       </c>
-      <c r="S9" s="3" t="n">
+      <c r="S9" s="2" t="n">
         <v>49.1</v>
       </c>
-      <c r="T9" s="3" t="n">
+      <c r="T9" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="U9" s="2" t="n">
         <v>198</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4747,12 +4741,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4766,62 +4760,60 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>11430</v>
+        <v>2611</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2474.6</v>
+        <v>5403</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2480.4</v>
+        <v>5418</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.28</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>48.04</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>56.02</v>
-      </c>
+        <v>6.85</v>
+      </c>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>12.85</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>4.03</v>
+        <v>3.19</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>4.42</v>
+        <v>3.72</v>
       </c>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="T43" s="2" t="n"/>
       <c r="U43" s="2" t="n">
-        <v>304</v>
+        <v>75</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>271</v>
+        <v>70</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>12.2</v>
+        <v>7.1</v>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -4846,12 +4838,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Sudeep Pharma Limited</t>
+          <t>Pearl Global Industries Limited</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4861,11 +4853,11 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nifty Chemicals</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>12487</v>
+        <v>11430</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -4876,51 +4868,47 @@
         <v>10</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1105.55</v>
+        <v>2474.6</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1108.4</v>
+        <v>2480.4</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>70.36</v>
+        <v>48.04</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>56.02</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>42.81</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>-1.41</v>
+        <v>4.03</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>6.68</v>
-      </c>
+        <v>4.42</v>
+      </c>
+      <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="T44" s="2" t="n">
-        <v>36.1</v>
-      </c>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="T44" s="2" t="n"/>
       <c r="U44" s="2" t="n">
-        <v>185</v>
+        <v>304</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>175</v>
+        <v>271</v>
       </c>
       <c r="W44" s="2" t="n">
-        <v>5.7</v>
+        <v>12.2</v>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
@@ -4949,12 +4937,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited</t>
+          <t>Sudeep Pharma Limited</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4964,62 +4952,66 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Chemicals</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>19721</v>
+        <v>12487</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>2089.6</v>
+        <v>1105.55</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2089.6</v>
+        <v>1108.4</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>50.7</v>
+        <v>70.36</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>60.76</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>120.9</v>
+        <v>42.81</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>4.03</v>
+        <v>-1.41</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R45" s="2" t="n"/>
+        <v>-0.85</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>6.68</v>
+      </c>
       <c r="S45" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="T45" s="2" t="n"/>
+        <v>44.2</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>36.1</v>
+      </c>
       <c r="U45" s="2" t="n">
-        <v>327</v>
+        <v>185</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>302</v>
+        <v>175</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
@@ -5048,12 +5040,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>Happy Forgings Limited</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5067,60 +5059,62 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1382</v>
+        <v>19721</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>165.42</v>
+        <v>2089.6</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>166.77</v>
+        <v>2089.6</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="N46" s="2" t="n"/>
+        <v>50.7</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>60.76</v>
+      </c>
       <c r="O46" s="2" t="n">
-        <v>46.35</v>
+        <v>120.9</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>11.16</v>
+        <v>4.03</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>11.94</v>
+        <v>4.42</v>
       </c>
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n">
-        <v>35.2</v>
+        <v>116.9</v>
       </c>
       <c r="T46" s="2" t="n"/>
       <c r="U46" s="2" t="n">
-        <v>58</v>
+        <v>327</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>50</v>
+        <v>302</v>
       </c>
       <c r="W46" s="2" t="n">
-        <v>16</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5145,12 +5139,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>GSP Crop Science Limited</t>
+          <t>Rajputana Stainless Limited</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5164,60 +5158,60 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>2774</v>
+        <v>1382</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>596.25</v>
+        <v>165.42</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>597.5</v>
+        <v>166.77</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>39.38</v>
+        <v>19.29</v>
       </c>
       <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n">
-        <v>67.37</v>
+        <v>46.35</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>12</v>
+        <v>11.16</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>12.8</v>
+        <v>11.94</v>
       </c>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n">
-        <v>55.4</v>
+        <v>35.2</v>
       </c>
       <c r="T47" s="2" t="n"/>
       <c r="U47" s="2" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="W47" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -5242,95 +5236,89 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>AAYUSHBULL</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>AAYUSH ART AND BULLION LIMITED</t>
+          <t>GSP Crop Science Limited</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1908</v>
+        <v>2774</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1245.9</v>
+        <v>596.25</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1247.65</v>
+        <v>597.5</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.21</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>12.25</v>
-      </c>
+        <v>39.38</v>
+      </c>
+      <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="n">
-        <v>32.63</v>
+        <v>67.37</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>4.03</v>
+        <v>12</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="T48" s="2" t="n">
-        <v>36.4</v>
-      </c>
+        <v>55.4</v>
+      </c>
+      <c r="T48" s="2" t="n"/>
       <c r="U48" s="2" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="W48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -5345,57 +5333,57 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>AAYUSHBULL</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Krishana Phoschem Limited</t>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>5895</v>
+        <v>1908</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
         <v>16</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>190.68</v>
+        <v>1245.9</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>190.68</v>
+        <v>1247.65</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>42.37</v>
+        <v>8.68</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>86.03</v>
+        <v>12.25</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>75.11</v>
+        <v>32.63</v>
       </c>
       <c r="P49" s="2" t="n">
         <v>4.03</v>
@@ -5403,19 +5391,23 @@
       <c r="Q49" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R49" s="2" t="n"/>
+      <c r="R49" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="S49" s="2" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="T49" s="2" t="n"/>
+        <v>28.6</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>36.4</v>
+      </c>
       <c r="U49" s="2" t="n">
-        <v>196</v>
+        <v>8</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="W49" s="2" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
@@ -5424,12 +5416,12 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -5444,12 +5436,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
+          <t>Krishana Phoschem Limited</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -5463,54 +5455,58 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>2611</v>
+        <v>5895</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5403</v>
+        <v>190.68</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5418</v>
+        <v>190.68</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="n"/>
-      <c r="N50" s="2" t="n"/>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>86.03</v>
+      </c>
       <c r="O50" s="2" t="n">
-        <v>7.34</v>
+        <v>75.11</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>1.94</v>
+        <v>4.03</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>2.06</v>
+        <v>4.42</v>
       </c>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n">
-        <v>5.4</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="T50" s="2" t="n"/>
       <c r="U50" s="2" t="n">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="V50" s="2" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="W50" s="2" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
@@ -5652,80 +5648,80 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ATH Radar - weekly screen</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr"/>
+      <c r="B1" s="4" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Run date</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>2026-08-15 (prices as of 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Universe</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>2126 NSE mainboard (EQ) + 1014 NSE Emerge SME</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Filters</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Within 2% of all-time-high close; TTM return above Nifty 500, Nifty Total Market, sector index (mainboard) / NIFTY SME EMERGE (SME); TTM PAT &gt;= every prior annual and rolling window (screener.in); mcap Rs 1,000-20,000 Cr</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Sort</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Newest entrant into the 2% ATH zone first; green rows new since previous run</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>3140 screened -&gt; 173 at ATH -&gt; 166 outperforming -&gt; 99 record PAT -&gt; 50 in mcap band</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>3140 screened -&gt; 162 at ATH -&gt; 160 outperforming -&gt; 99 record PAT -&gt; 50 in mcap band</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Caveats</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>SME price history since Jul-2024, unadjusted for corporate actions; PAT history limited to screener-visible years; mainboard prices split-adjusted (Yahoo). Factual screen - not investment advice</t>
         </is>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AA$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,12 +79,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -449,36 +455,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AB52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,105 +521,110 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Entered ATH Zone</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Days in Zone</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Last Close</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>% from ATH</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ATH Date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>3M Return %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>6M Return %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TTM Return %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Nifty 500 %</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Nifty TM %</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sector/SME %</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Alpha vs N500 pp</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Alpha vs Sector/SME pp</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TTM PAT (Rs Cr)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Prior Peak PAT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>PAT vs Peak %</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Latest Period</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>New This Week</t>
         </is>
@@ -645,77 +657,80 @@
       <c r="F2" s="2" t="n">
         <v>3608</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1731.15</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1731.15</v>
       </c>
       <c r="K2" s="2" t="n">
+        <v>1731.15</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>55.9</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>107.41</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>156.79</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="T2" s="2" t="n">
         <v>152.8</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="U2" s="2" t="n">
         <v>160.6</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>46</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>46</v>
       </c>
       <c r="W2" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -748,73 +763,76 @@
       <c r="F3" s="2" t="n">
         <v>8111</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>2532.5</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2532.5</v>
       </c>
       <c r="K3" s="2" t="n">
+        <v>2532.5</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>33.1</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>40.41</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>115.28</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n">
         <v>111.2</v>
       </c>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n">
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n">
         <v>211</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="W3" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="X3" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -847,77 +865,80 @@
       <c r="F4" s="2" t="n">
         <v>3956</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>1266.1</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>1284.85</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>-1.46</v>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.83</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>14.27</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>94.78</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="R4" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="S4" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="T4" s="2" t="n">
         <v>90.8</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="U4" s="2" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="V4" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="W4" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="X4" s="2" t="n">
         <v>51.6</v>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -950,77 +971,80 @@
       <c r="F5" s="2" t="n">
         <v>9654</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>792.05</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>792.05</v>
       </c>
       <c r="K5" s="2" t="n">
+        <v>792.05</v>
+      </c>
+      <c r="L5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>28.85</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="O5" s="2" t="n">
         <v>25.04</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>85.04000000000001</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="T5" s="2" t="n">
+      <c r="U5" s="2" t="n">
         <v>63.9</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="V5" s="2" t="n">
         <v>268</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="W5" s="2" t="n">
         <v>251</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="X5" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1053,73 +1077,76 @@
       <c r="F6" s="2" t="n">
         <v>4047</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>1073.45</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>1094.5</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>-1.92</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>50.21</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>75.76000000000001</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n">
         <v>71.7</v>
       </c>
-      <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="n">
+      <c r="U6" s="2" t="n"/>
+      <c r="V6" s="2" t="n">
         <v>25.7</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="W6" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="X6" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1152,77 +1179,80 @@
       <c r="F7" s="2" t="n">
         <v>4311</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>1502.05</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1502.05</v>
       </c>
       <c r="K7" s="2" t="n">
+        <v>1502.05</v>
+      </c>
+      <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>66.34</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="O7" s="2" t="n">
         <v>65.04000000000001</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>68.75</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>64.7</v>
       </c>
-      <c r="T7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>72.5</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="V7" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="W7" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="X7" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1255,73 +1285,76 @@
       <c r="F8" s="2" t="n">
         <v>4496</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>599.45</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="K8" s="2" t="n">
         <v>601.4</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>-0.32</v>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n">
+      <c r="N8" s="2" t="n">
         <v>7.02</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>41.33</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>51.22</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n">
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n">
         <v>47.2</v>
       </c>
-      <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n">
+      <c r="U8" s="2" t="n"/>
+      <c r="V8" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="W8" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="W8" s="2" t="n">
+      <c r="X8" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1354,77 +1387,80 @@
       <c r="F9" s="2" t="n">
         <v>13071</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>2137.1</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>2159.7</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-1.05</v>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>20.24</v>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>34.15</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>48.57</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>-0.55</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>0.09</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>12.2</v>
       </c>
-      <c r="S9" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>49.1</v>
       </c>
-      <c r="T9" s="2" t="n">
+      <c r="U9" s="2" t="n">
         <v>36.4</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="V9" s="2" t="n">
         <v>198</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="W9" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="W9" s="2" t="n">
+      <c r="X9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
+      <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1457,77 +1493,80 @@
       <c r="F10" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="I10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>792.45</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>792.45</v>
       </c>
       <c r="K10" s="2" t="n">
+        <v>792.45</v>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>27.95</v>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="O10" s="2" t="n">
         <v>2.32</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>31.69</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="R10" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R10" s="2" t="n">
+      <c r="S10" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S10" s="2" t="n">
+      <c r="T10" s="2" t="n">
         <v>27.7</v>
       </c>
-      <c r="T10" s="2" t="n">
+      <c r="U10" s="2" t="n">
         <v>35.5</v>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="V10" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="V10" s="2" t="n">
+      <c r="W10" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="W10" s="2" t="n">
+      <c r="X10" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1560,77 +1599,80 @@
       <c r="F11" s="2" t="n">
         <v>10965</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="I11" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>1737.1</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1737.1</v>
       </c>
       <c r="K11" s="2" t="n">
+        <v>1737.1</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>33.05</v>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>23.17</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="P11" s="2" t="n">
         <v>26.21</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="R11" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="S11" s="2" t="n">
         <v>-11.05</v>
       </c>
-      <c r="S11" s="2" t="n">
+      <c r="T11" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="T11" s="2" t="n">
+      <c r="U11" s="2" t="n">
         <v>37.3</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="V11" s="2" t="n">
         <v>258</v>
       </c>
-      <c r="V11" s="2" t="n">
+      <c r="W11" s="2" t="n">
         <v>226</v>
       </c>
-      <c r="W11" s="2" t="n">
+      <c r="X11" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="X11" s="2" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1663,73 +1705,76 @@
       <c r="F12" s="2" t="n">
         <v>6926</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="I12" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>2730.8</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2730.8</v>
       </c>
       <c r="K12" s="2" t="n">
+        <v>2730.8</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
+      <c r="N12" s="2" t="n">
         <v>38.07</v>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="O12" s="2" t="n">
         <v>60.83</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>227.22</v>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="R12" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2" t="n">
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n">
         <v>223.2</v>
       </c>
-      <c r="T12" s="2" t="n"/>
-      <c r="U12" s="2" t="n">
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="W12" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="W12" s="2" t="n">
+      <c r="X12" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z12" s="2" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1762,73 +1807,76 @@
       <c r="F13" s="2" t="n">
         <v>6585</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>1433.9</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1433.9</v>
       </c>
       <c r="K13" s="2" t="n">
+        <v>1433.9</v>
+      </c>
+      <c r="L13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="N13" s="2" t="n">
         <v>73.7</v>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>94.84</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="P13" s="2" t="n">
         <v>137.2</v>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="R13" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R13" s="2" t="n"/>
-      <c r="S13" s="2" t="n">
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="n">
         <v>133.2</v>
       </c>
-      <c r="T13" s="2" t="n"/>
-      <c r="U13" s="2" t="n">
+      <c r="U13" s="2" t="n"/>
+      <c r="V13" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="V13" s="2" t="n">
+      <c r="W13" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="W13" s="2" t="n">
+      <c r="X13" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="X13" s="2" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y13" s="2" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1861,73 +1909,76 @@
       <c r="F14" s="2" t="n">
         <v>5188</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>370.7</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>371.2</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>-0.13</v>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="N14" s="2" t="n">
         <v>69.45999999999999</v>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>102.89</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>123.57</v>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="R14" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n">
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n">
         <v>119.5</v>
       </c>
-      <c r="T14" s="2" t="n"/>
-      <c r="U14" s="2" t="n">
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="V14" s="2" t="n">
+      <c r="W14" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="W14" s="2" t="n">
+      <c r="X14" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="X14" s="2" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1960,73 +2011,76 @@
       <c r="F15" s="2" t="n">
         <v>6172</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>3642</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>3651.2</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="L15" s="2" t="n">
         <v>-0.25</v>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="N15" s="2" t="n">
         <v>37.24</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="O15" s="2" t="n">
         <v>64.17</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>119.28</v>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="R15" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n">
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="n">
         <v>115.2</v>
       </c>
-      <c r="T15" s="2" t="n"/>
-      <c r="U15" s="2" t="n">
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="V15" s="2" t="n">
+      <c r="W15" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="W15" s="2" t="n">
+      <c r="X15" s="2" t="n">
         <v>12.7</v>
       </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2059,73 +2113,76 @@
       <c r="F16" s="2" t="n">
         <v>17552</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>2717.8</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2717.8</v>
       </c>
       <c r="K16" s="2" t="n">
+        <v>2717.8</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>29.53</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>72.11</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>75.25</v>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="R16" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n">
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n">
         <v>71.2</v>
       </c>
-      <c r="T16" s="2" t="n"/>
-      <c r="U16" s="2" t="n">
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="V16" s="2" t="n">
+      <c r="W16" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="W16" s="2" t="n">
+      <c r="X16" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="X16" s="2" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z16" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2158,73 +2215,76 @@
       <c r="F17" s="2" t="n">
         <v>3561</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>351.85</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>354.15</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>-0.65</v>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="N17" s="2" t="n">
         <v>24.28</v>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="O17" s="2" t="n">
         <v>56.9</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>69.08</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="R17" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R17" s="2" t="n"/>
-      <c r="S17" s="2" t="n">
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="T17" s="2" t="n"/>
-      <c r="U17" s="2" t="n">
-        <v>91</v>
-      </c>
+      <c r="U17" s="2" t="n"/>
       <c r="V17" s="2" t="n">
         <v>91</v>
       </c>
       <c r="W17" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="X17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2257,77 +2317,80 @@
       <c r="F18" s="2" t="n">
         <v>2142</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>1021.35</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>1023.7</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>-0.23</v>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="N18" s="2" t="n">
         <v>35.95</v>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>92.91</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>63.94</v>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="R18" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="S18" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="T18" s="2" t="n">
         <v>59.9</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="U18" s="2" t="n">
         <v>67.7</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>39</v>
       </c>
       <c r="V18" s="2" t="n">
         <v>39</v>
       </c>
       <c r="W18" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="X18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="Z18" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
+      <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2360,77 +2423,80 @@
       <c r="F19" s="2" t="n">
         <v>17025</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="I19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>1386.7</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>1393.6</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n">
+      <c r="N19" s="2" t="n">
         <v>32.75</v>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="O19" s="2" t="n">
         <v>50.76</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>46.88</v>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="R19" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="S19" s="2" t="n">
         <v>12.7</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="T19" s="2" t="n">
         <v>42.9</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="U19" s="2" t="n">
         <v>34.2</v>
       </c>
-      <c r="U19" s="2" t="n">
+      <c r="V19" s="2" t="n">
         <v>603</v>
       </c>
-      <c r="V19" s="2" t="n">
+      <c r="W19" s="2" t="n">
         <v>565</v>
       </c>
-      <c r="W19" s="2" t="n">
+      <c r="X19" s="2" t="n">
         <v>6.7</v>
       </c>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
+      <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2463,73 +2529,76 @@
       <c r="F20" s="2" t="n">
         <v>17034</v>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="I20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>510.05</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>518</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>-1.53</v>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="N20" s="2" t="n">
         <v>23.16</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="O20" s="2" t="n">
         <v>14.55</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>16.13</v>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="R20" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R20" s="2" t="n"/>
-      <c r="S20" s="2" t="n">
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n">
         <v>12.1</v>
       </c>
-      <c r="T20" s="2" t="n"/>
-      <c r="U20" s="2" t="n">
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n">
         <v>444</v>
       </c>
-      <c r="V20" s="2" t="n">
+      <c r="W20" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="W20" s="2" t="n">
+      <c r="X20" s="2" t="n">
         <v>9.9</v>
       </c>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
+      <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2562,77 +2631,80 @@
       <c r="F21" s="2" t="n">
         <v>2202</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="I21" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>852</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>852</v>
       </c>
       <c r="K21" s="2" t="n">
+        <v>852</v>
+      </c>
+      <c r="L21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>126.75</v>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="O21" s="2" t="n">
         <v>182.07</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>176.04</v>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="R21" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="S21" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="T21" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="T21" s="2" t="n">
+      <c r="U21" s="2" t="n">
         <v>179.8</v>
       </c>
-      <c r="U21" s="2" t="n">
+      <c r="V21" s="2" t="n">
         <v>31.5</v>
       </c>
-      <c r="V21" s="2" t="n">
+      <c r="W21" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="W21" s="2" t="n">
+      <c r="X21" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="X21" s="2" t="inlineStr">
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
+      <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2665,77 +2737,80 @@
       <c r="F22" s="2" t="n">
         <v>2065</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="I22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>950.25</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>967.6</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>-1.79</v>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="N22" s="2" t="n">
         <v>81.73</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>105.55</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>137.56</v>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="R22" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="S22" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="T22" s="2" t="n">
         <v>133.5</v>
       </c>
-      <c r="T22" s="2" t="n">
+      <c r="U22" s="2" t="n">
         <v>141.4</v>
       </c>
-      <c r="U22" s="2" t="n">
+      <c r="V22" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="V22" s="2" t="n">
+      <c r="W22" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="W22" s="2" t="n">
+      <c r="X22" s="2" t="n">
         <v>26.1</v>
       </c>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
+      <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2768,73 +2843,76 @@
       <c r="F23" s="2" t="n">
         <v>3979</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="I23" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>1301.05</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1301.05</v>
       </c>
       <c r="K23" s="2" t="n">
+        <v>1301.05</v>
+      </c>
+      <c r="L23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n">
+      <c r="N23" s="2" t="n">
         <v>95.94</v>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="O23" s="2" t="n">
         <v>74.73999999999999</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="P23" s="2" t="n">
         <v>101.34</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="R23" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n">
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n">
         <v>97.3</v>
       </c>
-      <c r="T23" s="2" t="n"/>
-      <c r="U23" s="2" t="n">
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="V23" s="2" t="n">
+      <c r="W23" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="W23" s="2" t="n">
+      <c r="X23" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2867,77 +2945,80 @@
       <c r="F24" s="2" t="n">
         <v>19789</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="I24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>4492.4</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="K24" s="2" t="n">
         <v>4524.4</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>-0.71</v>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="N24" s="2" t="n">
         <v>32.69</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="O24" s="2" t="n">
         <v>45.67</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>82.65000000000001</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q24" s="2" t="n">
+      <c r="R24" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="S24" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="T24" s="2" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="T24" s="2" t="n">
+      <c r="U24" s="2" t="n">
         <v>61.6</v>
       </c>
-      <c r="U24" s="2" t="n">
+      <c r="V24" s="2" t="n">
         <v>575</v>
       </c>
-      <c r="V24" s="2" t="n">
+      <c r="W24" s="2" t="n">
         <v>562</v>
       </c>
-      <c r="W24" s="2" t="n">
+      <c r="X24" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2970,77 +3051,80 @@
       <c r="F25" s="2" t="n">
         <v>11714</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="I25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="J25" s="2" t="n">
         <v>309.65</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="K25" s="2" t="n">
         <v>313.7</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="L25" s="2" t="n">
         <v>-1.29</v>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="N25" s="2" t="n">
         <v>25.82</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="O25" s="2" t="n">
         <v>52.75</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="P25" s="2" t="n">
         <v>82.26000000000001</v>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q25" s="2" t="n">
+      <c r="R25" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="S25" s="2" t="n">
         <v>-0.45</v>
       </c>
-      <c r="S25" s="2" t="n">
+      <c r="T25" s="2" t="n">
         <v>78.2</v>
       </c>
-      <c r="T25" s="2" t="n">
+      <c r="U25" s="2" t="n">
         <v>82.7</v>
       </c>
-      <c r="U25" s="2" t="n">
+      <c r="V25" s="2" t="n">
         <v>1437</v>
       </c>
-      <c r="V25" s="2" t="n">
+      <c r="W25" s="2" t="n">
         <v>1341</v>
       </c>
-      <c r="W25" s="2" t="n">
+      <c r="X25" s="2" t="n">
         <v>7.2</v>
       </c>
-      <c r="X25" s="2" t="inlineStr">
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3073,73 +3157,76 @@
       <c r="F26" s="2" t="n">
         <v>9611</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>1468.3</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1468.3</v>
       </c>
       <c r="K26" s="2" t="n">
+        <v>1468.3</v>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="N26" s="2" t="n">
         <v>25.22</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="O26" s="2" t="n">
         <v>105.3</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>72.13</v>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q26" s="2" t="n">
+      <c r="R26" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R26" s="2" t="n"/>
-      <c r="S26" s="2" t="n">
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="T26" s="2" t="n"/>
-      <c r="U26" s="2" t="n">
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="V26" s="2" t="n">
+      <c r="W26" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="W26" s="2" t="n">
+      <c r="X26" s="2" t="n">
         <v>27.6</v>
       </c>
-      <c r="X26" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
+      <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3172,73 +3259,76 @@
       <c r="F27" s="2" t="n">
         <v>4435</v>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="I27" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>475.05</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>475.05</v>
       </c>
       <c r="K27" s="2" t="n">
+        <v>475.05</v>
+      </c>
+      <c r="L27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n">
+      <c r="N27" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="O27" s="2" t="n">
         <v>52.24</v>
       </c>
-      <c r="O27" s="2" t="n">
+      <c r="P27" s="2" t="n">
         <v>39.18</v>
       </c>
-      <c r="P27" s="2" t="n">
+      <c r="Q27" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q27" s="2" t="n">
+      <c r="R27" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R27" s="2" t="n"/>
-      <c r="S27" s="2" t="n">
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n">
         <v>35.1</v>
       </c>
-      <c r="T27" s="2" t="n"/>
-      <c r="U27" s="2" t="n">
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="V27" s="2" t="n">
+      <c r="W27" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="W27" s="2" t="n">
+      <c r="X27" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="X27" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3271,73 +3361,76 @@
       <c r="F28" s="2" t="n">
         <v>12967</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="J28" s="2" t="n">
         <v>1940.8</v>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="K28" s="2" t="n">
         <v>1965.3</v>
       </c>
-      <c r="K28" s="2" t="n">
+      <c r="L28" s="2" t="n">
         <v>-1.25</v>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n">
+      <c r="N28" s="2" t="n">
         <v>46.69</v>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="O28" s="2" t="n">
         <v>84.13</v>
       </c>
-      <c r="O28" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>131.67</v>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q28" s="2" t="n">
+      <c r="R28" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n">
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n">
         <v>127.6</v>
       </c>
-      <c r="T28" s="2" t="n"/>
-      <c r="U28" s="2" t="n">
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="V28" s="2" t="n">
+      <c r="W28" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="W28" s="2" t="n">
+      <c r="X28" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3370,73 +3463,76 @@
       <c r="F29" s="2" t="n">
         <v>6805</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="J29" s="2" t="n">
         <v>1477.7</v>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="K29" s="2" t="n">
         <v>1492.4</v>
       </c>
-      <c r="K29" s="2" t="n">
+      <c r="L29" s="2" t="n">
         <v>-0.98</v>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n">
+      <c r="N29" s="2" t="n">
         <v>40.69</v>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="O29" s="2" t="n">
         <v>88.59</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="P29" s="2" t="n">
         <v>118.84</v>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="Q29" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q29" s="2" t="n">
+      <c r="R29" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n">
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="n">
         <v>114.8</v>
       </c>
-      <c r="T29" s="2" t="n"/>
-      <c r="U29" s="2" t="n">
+      <c r="U29" s="2" t="n"/>
+      <c r="V29" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="V29" s="2" t="n">
+      <c r="W29" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="W29" s="2" t="n">
+      <c r="X29" s="2" t="n">
         <v>7.4</v>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3469,73 +3565,76 @@
       <c r="F30" s="2" t="n">
         <v>1867</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="I30" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>1243</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>1243</v>
       </c>
       <c r="K30" s="2" t="n">
+        <v>1243</v>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n">
+      <c r="N30" s="2" t="n">
         <v>95.15000000000001</v>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="O30" s="2" t="n">
         <v>89.94</v>
       </c>
-      <c r="O30" s="2" t="n">
+      <c r="P30" s="2" t="n">
         <v>99.76000000000001</v>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="Q30" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q30" s="2" t="n">
+      <c r="R30" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n">
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n">
         <v>95.7</v>
       </c>
-      <c r="T30" s="2" t="n"/>
-      <c r="U30" s="2" t="n">
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="V30" s="2" t="n">
+      <c r="W30" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="W30" s="2" t="n">
+      <c r="X30" s="2" t="n">
         <v>5.7</v>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3568,73 +3667,76 @@
       <c r="F31" s="2" t="n">
         <v>5953</v>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="J31" s="2" t="n">
         <v>298.4</v>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="K31" s="2" t="n">
         <v>300.05</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="L31" s="2" t="n">
         <v>-0.55</v>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n">
+      <c r="N31" s="2" t="n">
         <v>118.88</v>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="O31" s="2" t="n">
         <v>127.08</v>
       </c>
-      <c r="O31" s="2" t="n">
+      <c r="P31" s="2" t="n">
         <v>84.17</v>
       </c>
-      <c r="P31" s="2" t="n">
+      <c r="Q31" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q31" s="2" t="n">
+      <c r="R31" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R31" s="2" t="n"/>
-      <c r="S31" s="2" t="n">
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="T31" s="2" t="n"/>
-      <c r="U31" s="2" t="n">
+      <c r="U31" s="2" t="n"/>
+      <c r="V31" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="V31" s="2" t="n">
+      <c r="W31" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="W31" s="2" t="n">
+      <c r="X31" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="X31" s="2" t="inlineStr">
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="AA31" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3667,73 +3769,76 @@
       <c r="F32" s="2" t="n">
         <v>14742</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="I32" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>251.33</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>251.33</v>
       </c>
       <c r="K32" s="2" t="n">
+        <v>251.33</v>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="N32" s="2" t="n">
         <v>33.28</v>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="O32" s="2" t="n">
         <v>101.5</v>
       </c>
-      <c r="O32" s="2" t="n">
+      <c r="P32" s="2" t="n">
         <v>128.52</v>
       </c>
-      <c r="P32" s="2" t="n">
+      <c r="Q32" s="2" t="n">
         <v>2.22</v>
       </c>
-      <c r="Q32" s="2" t="n">
+      <c r="R32" s="2" t="n">
         <v>3.03</v>
       </c>
-      <c r="R32" s="2" t="n"/>
-      <c r="S32" s="2" t="n">
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n">
         <v>126.3</v>
       </c>
-      <c r="T32" s="2" t="n"/>
-      <c r="U32" s="2" t="n">
+      <c r="U32" s="2" t="n"/>
+      <c r="V32" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="V32" s="2" t="n">
+      <c r="W32" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="W32" s="2" t="n">
+      <c r="X32" s="2" t="n">
         <v>50.9</v>
       </c>
-      <c r="X32" s="2" t="inlineStr">
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3766,71 +3871,74 @@
       <c r="F33" s="2" t="n">
         <v>13927</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="I33" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>3152.9</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>3152.9</v>
       </c>
       <c r="K33" s="2" t="n">
+        <v>3152.9</v>
+      </c>
+      <c r="L33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n">
+      <c r="N33" s="2" t="n">
         <v>59.08</v>
       </c>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n">
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n">
         <v>117.28</v>
       </c>
-      <c r="P33" s="2" t="n">
+      <c r="Q33" s="2" t="n">
         <v>7.04</v>
       </c>
-      <c r="Q33" s="2" t="n">
+      <c r="R33" s="2" t="n">
         <v>7.83</v>
       </c>
-      <c r="R33" s="2" t="n"/>
-      <c r="S33" s="2" t="n">
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n">
         <v>110.2</v>
       </c>
-      <c r="T33" s="2" t="n"/>
-      <c r="U33" s="2" t="n">
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="V33" s="2" t="n">
+      <c r="W33" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="W33" s="2" t="n">
+      <c r="X33" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3863,73 +3971,76 @@
       <c r="F34" s="2" t="n">
         <v>7381</v>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>168.46</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>168.46</v>
       </c>
       <c r="K34" s="2" t="n">
+        <v>168.46</v>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="N34" s="2" t="n">
         <v>57.35</v>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="O34" s="2" t="n">
         <v>81.23999999999999</v>
       </c>
-      <c r="O34" s="2" t="n">
+      <c r="P34" s="2" t="n">
         <v>99.56999999999999</v>
       </c>
-      <c r="P34" s="2" t="n">
+      <c r="Q34" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q34" s="2" t="n">
+      <c r="R34" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="n">
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n">
         <v>95.5</v>
       </c>
-      <c r="T34" s="2" t="n"/>
-      <c r="U34" s="2" t="n">
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="V34" s="2" t="n">
+      <c r="W34" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="W34" s="2" t="n">
+      <c r="X34" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="X34" s="2" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3962,73 +4073,76 @@
       <c r="F35" s="2" t="n">
         <v>5572</v>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>7749</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="K35" s="2" t="n">
         <v>7781</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="L35" s="2" t="n">
         <v>-0.41</v>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="N35" s="2" t="n">
         <v>84.89</v>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="O35" s="2" t="n">
         <v>50.78</v>
       </c>
-      <c r="O35" s="2" t="n">
+      <c r="P35" s="2" t="n">
         <v>58.01</v>
       </c>
-      <c r="P35" s="2" t="n">
+      <c r="Q35" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q35" s="2" t="n">
+      <c r="R35" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R35" s="2" t="n"/>
-      <c r="S35" s="2" t="n">
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="T35" s="2" t="n"/>
-      <c r="U35" s="2" t="n">
+      <c r="U35" s="2" t="n"/>
+      <c r="V35" s="2" t="n">
         <v>219</v>
       </c>
-      <c r="V35" s="2" t="n">
+      <c r="W35" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="W35" s="2" t="n">
+      <c r="X35" s="2" t="n">
         <v>40.4</v>
       </c>
-      <c r="X35" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
+      <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4061,73 +4175,76 @@
       <c r="F36" s="2" t="n">
         <v>1791</v>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>588.4</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>588.4</v>
       </c>
       <c r="K36" s="2" t="n">
+        <v>588.4</v>
+      </c>
+      <c r="L36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="N36" s="2" t="n">
         <v>79.5</v>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="O36" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="P36" s="2" t="n">
         <v>140.29</v>
       </c>
-      <c r="P36" s="2" t="n">
+      <c r="Q36" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q36" s="2" t="n">
+      <c r="R36" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="n">
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="n">
         <v>136.3</v>
       </c>
-      <c r="T36" s="2" t="n"/>
-      <c r="U36" s="2" t="n">
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="n">
         <v>30.5</v>
       </c>
-      <c r="V36" s="2" t="n">
+      <c r="W36" s="2" t="n">
         <v>28.1</v>
       </c>
-      <c r="W36" s="2" t="n">
+      <c r="X36" s="2" t="n">
         <v>8.5</v>
       </c>
-      <c r="X36" s="2" t="inlineStr">
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4160,77 +4277,80 @@
       <c r="F37" s="2" t="n">
         <v>1399</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="I37" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>583</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>583</v>
       </c>
       <c r="K37" s="2" t="n">
+        <v>583</v>
+      </c>
+      <c r="L37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n">
+      <c r="N37" s="2" t="n">
         <v>32.12</v>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="O37" s="2" t="n">
         <v>81.14</v>
       </c>
-      <c r="O37" s="2" t="n">
+      <c r="P37" s="2" t="n">
         <v>100.58</v>
       </c>
-      <c r="P37" s="2" t="n">
+      <c r="Q37" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q37" s="2" t="n">
+      <c r="R37" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R37" s="2" t="n">
+      <c r="S37" s="2" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S37" s="2" t="n">
+      <c r="T37" s="2" t="n">
         <v>96.5</v>
       </c>
-      <c r="T37" s="2" t="n">
+      <c r="U37" s="2" t="n">
         <v>104.4</v>
-      </c>
-      <c r="U37" s="2" t="n">
-        <v>44</v>
       </c>
       <c r="V37" s="2" t="n">
         <v>44</v>
       </c>
       <c r="W37" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="X37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
+      <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4263,73 +4383,76 @@
       <c r="F38" s="2" t="n">
         <v>6969</v>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="I38" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>1028.6</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1028.6</v>
       </c>
       <c r="K38" s="2" t="n">
+        <v>1028.6</v>
+      </c>
+      <c r="L38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="N38" s="2" t="n">
         <v>61.92</v>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="O38" s="2" t="n">
         <v>184.97</v>
       </c>
-      <c r="O38" s="2" t="n">
+      <c r="P38" s="2" t="n">
         <v>189.75</v>
       </c>
-      <c r="P38" s="2" t="n">
+      <c r="Q38" s="2" t="n">
         <v>-1.26</v>
       </c>
-      <c r="Q38" s="2" t="n">
+      <c r="R38" s="2" t="n">
         <v>-0.63</v>
       </c>
-      <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="n">
+      <c r="S38" s="2" t="n"/>
+      <c r="T38" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="T38" s="2" t="n"/>
-      <c r="U38" s="2" t="n">
+      <c r="U38" s="2" t="n"/>
+      <c r="V38" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="V38" s="2" t="n">
+      <c r="W38" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="W38" s="2" t="n">
+      <c r="X38" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="X38" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y38" s="2" t="inlineStr">
+      <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z38" s="2" t="inlineStr">
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
+      <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4362,73 +4485,76 @@
       <c r="F39" s="2" t="n">
         <v>9274</v>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="I39" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="J39" s="2" t="n">
         <v>735.85</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="K39" s="2" t="n">
         <v>747.15</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="L39" s="2" t="n">
         <v>-1.51</v>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n">
+      <c r="N39" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="O39" s="2" t="n">
         <v>75.66</v>
       </c>
-      <c r="O39" s="2" t="n">
+      <c r="P39" s="2" t="n">
         <v>105.49</v>
       </c>
-      <c r="P39" s="2" t="n">
+      <c r="Q39" s="2" t="n">
         <v>1.74</v>
       </c>
-      <c r="Q39" s="2" t="n">
+      <c r="R39" s="2" t="n">
         <v>2.1</v>
       </c>
-      <c r="R39" s="2" t="n"/>
-      <c r="S39" s="2" t="n">
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n">
         <v>103.8</v>
       </c>
-      <c r="T39" s="2" t="n"/>
-      <c r="U39" s="2" t="n">
+      <c r="U39" s="2" t="n"/>
+      <c r="V39" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="V39" s="2" t="n">
+      <c r="W39" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="W39" s="2" t="n">
+      <c r="X39" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="Y39" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Z39" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4461,73 +4587,76 @@
       <c r="F40" s="2" t="n">
         <v>1163</v>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>288.33</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>288.33</v>
       </c>
       <c r="K40" s="2" t="n">
+        <v>288.33</v>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n">
+      <c r="N40" s="2" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="O40" s="2" t="n">
         <v>58.46</v>
       </c>
-      <c r="O40" s="2" t="n">
+      <c r="P40" s="2" t="n">
         <v>103.74</v>
       </c>
-      <c r="P40" s="2" t="n">
+      <c r="Q40" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q40" s="2" t="n">
+      <c r="R40" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R40" s="2" t="n"/>
-      <c r="S40" s="2" t="n">
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="n">
         <v>99.7</v>
       </c>
-      <c r="T40" s="2" t="n"/>
-      <c r="U40" s="2" t="n">
+      <c r="U40" s="2" t="n"/>
+      <c r="V40" s="2" t="n">
         <v>29.7</v>
       </c>
-      <c r="V40" s="2" t="n">
+      <c r="W40" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="2" t="n">
+      <c r="X40" s="2" t="n">
         <v>6.1</v>
       </c>
-      <c r="X40" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y40" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z40" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
+      <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4560,77 +4689,80 @@
       <c r="F41" s="2" t="n">
         <v>16077</v>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>822</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>822</v>
       </c>
       <c r="K41" s="2" t="n">
+        <v>822</v>
+      </c>
+      <c r="L41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n">
+      <c r="N41" s="2" t="n">
         <v>71.81999999999999</v>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="O41" s="2" t="n">
         <v>151.53</v>
       </c>
-      <c r="O41" s="2" t="n">
+      <c r="P41" s="2" t="n">
         <v>80.93000000000001</v>
       </c>
-      <c r="P41" s="2" t="n">
+      <c r="Q41" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q41" s="2" t="n">
+      <c r="R41" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R41" s="2" t="n">
+      <c r="S41" s="2" t="n">
         <v>12.7</v>
       </c>
-      <c r="S41" s="2" t="n">
+      <c r="T41" s="2" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="T41" s="2" t="n">
+      <c r="U41" s="2" t="n">
         <v>68.2</v>
       </c>
-      <c r="U41" s="2" t="n">
+      <c r="V41" s="2" t="n">
         <v>298</v>
       </c>
-      <c r="V41" s="2" t="n">
+      <c r="W41" s="2" t="n">
         <v>244</v>
       </c>
-      <c r="W41" s="2" t="n">
+      <c r="X41" s="2" t="n">
         <v>22.1</v>
       </c>
-      <c r="X41" s="2" t="inlineStr">
+      <c r="Y41" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
+      <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4663,73 +4795,76 @@
       <c r="F42" s="2" t="n">
         <v>4834</v>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="J42" s="2" t="n">
         <v>3930.2</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="K42" s="2" t="n">
         <v>3945.9</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="L42" s="2" t="n">
         <v>-0.4</v>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n">
+      <c r="N42" s="2" t="n">
         <v>74.91</v>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="O42" s="2" t="n">
         <v>70.94</v>
       </c>
-      <c r="O42" s="2" t="n">
+      <c r="P42" s="2" t="n">
         <v>51.66</v>
       </c>
-      <c r="P42" s="2" t="n">
+      <c r="Q42" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q42" s="2" t="n">
+      <c r="R42" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R42" s="2" t="n"/>
-      <c r="S42" s="2" t="n">
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="n">
         <v>47.6</v>
       </c>
-      <c r="T42" s="2" t="n"/>
-      <c r="U42" s="2" t="n">
+      <c r="U42" s="2" t="n"/>
+      <c r="V42" s="2" t="n">
         <v>151</v>
       </c>
-      <c r="V42" s="2" t="n">
+      <c r="W42" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="W42" s="2" t="n">
+      <c r="X42" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="X42" s="2" t="inlineStr">
+      <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="Z42" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4741,12 +4876,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
+          <t>Pearl Global Industries Limited</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4760,73 +4895,78 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2611</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>9</v>
+        <v>11430</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>5403</v>
+        <v>10</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5418</v>
+        <v>2474.6</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="N43" s="2" t="n"/>
+        <v>2480.4</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>48.04</v>
+      </c>
       <c r="O43" s="2" t="n">
-        <v>12.85</v>
+        <v>56.02</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>3.19</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R43" s="2" t="n"/>
-      <c r="S43" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="T43" s="2" t="n"/>
-      <c r="U43" s="2" t="n">
-        <v>75</v>
-      </c>
+        <v>4.03</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="U43" s="2" t="n"/>
       <c r="V43" s="2" t="n">
-        <v>70</v>
+        <v>304</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
+        <v>271</v>
+      </c>
+      <c r="X43" s="2" t="n">
+        <v>12.2</v>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z43" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4838,12 +4978,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Limited</t>
+          <t>Sudeep Pharma Limited</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4853,79 +4993,86 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Chemicals</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>11430</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+        <v>12487</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="I44" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>2474.6</v>
-      </c>
       <c r="J44" s="2" t="n">
-        <v>2480.4</v>
+        <v>1105.55</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>48.04</v>
+        <v>1108.4</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>56.02</v>
+        <v>70.36</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>4.03</v>
+        <v>42.81</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R44" s="2" t="n"/>
+        <v>-1.41</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>-0.85</v>
+      </c>
       <c r="S44" s="2" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="T44" s="2" t="n"/>
+        <v>6.68</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>44.2</v>
+      </c>
       <c r="U44" s="2" t="n">
-        <v>304</v>
+        <v>36.1</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>271</v>
+        <v>185</v>
       </c>
       <c r="W44" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
+        <v>175</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y44" s="2" t="inlineStr">
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z44" s="2" t="inlineStr">
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
+      <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4937,12 +5084,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Sudeep Pharma Limited</t>
+          <t>Happy Forgings Limited</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4952,83 +5099,82 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Nifty Chemicals</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>12487</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>10</v>
+        <v>19721</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1105.55</v>
+        <v>12</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1108.4</v>
+        <v>2089.6</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>70.36</v>
+        <v>2089.6</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>42.81</v>
+        <v>60.76</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>-1.41</v>
+        <v>120.9</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>-0.85</v>
+        <v>4.03</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="S45" s="2" t="n">
-        <v>44.2</v>
-      </c>
+        <v>4.42</v>
+      </c>
+      <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="U45" s="2" t="n">
-        <v>185</v>
-      </c>
+        <v>116.9</v>
+      </c>
+      <c r="U45" s="2" t="n"/>
       <c r="V45" s="2" t="n">
-        <v>175</v>
+        <v>327</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
+        <v>302</v>
+      </c>
+      <c r="X45" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="Z45" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
+      <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5040,12 +5186,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited</t>
+          <t>Rajputana Stainless Limited</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5059,75 +5205,76 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>19721</v>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>12</v>
+        <v>1382</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2089.6</v>
+        <v>13</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2089.6</v>
+        <v>165.42</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>50.7</v>
+        <v>166.77</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>60.76</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>120.9</v>
-      </c>
+        <v>19.29</v>
+      </c>
+      <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="n">
-        <v>4.03</v>
+        <v>46.35</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R46" s="2" t="n"/>
-      <c r="S46" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n">
-        <v>327</v>
-      </c>
+        <v>11.16</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="U46" s="2" t="n"/>
       <c r="V46" s="2" t="n">
-        <v>302</v>
+        <v>58</v>
       </c>
       <c r="W46" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="AA46" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5139,12 +5286,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>GSP Crop Science Limited</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5158,73 +5305,76 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>1382</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>13</v>
+        <v>2774</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>165.42</v>
+        <v>15</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>166.77</v>
+        <v>596.25</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n">
-        <v>46.35</v>
-      </c>
+        <v>597.5</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="n">
-        <v>11.16</v>
+        <v>67.37</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="R47" s="2" t="n"/>
-      <c r="S47" s="2" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="T47" s="2" t="n"/>
-      <c r="U47" s="2" t="n">
-        <v>58</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="S47" s="2" t="n"/>
+      <c r="T47" s="2" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="U47" s="2" t="n"/>
       <c r="V47" s="2" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="W47" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="X47" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="X47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z47" s="2" t="inlineStr">
+      <c r="AA47" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
+      <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5236,92 +5386,101 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>AAYUSHBULL</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>GSP Crop Science Limited</t>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>2774</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>14</v>
+        <v>1908</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>596.25</v>
+        <v>16</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>597.5</v>
+        <v>1245.9</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>39.38</v>
-      </c>
-      <c r="N48" s="2" t="n"/>
+        <v>1247.65</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>8.68</v>
+      </c>
       <c r="O48" s="2" t="n">
-        <v>67.37</v>
+        <v>12.25</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>12</v>
+        <v>32.63</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="R48" s="2" t="n"/>
+        <v>4.03</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>4.42</v>
+      </c>
       <c r="S48" s="2" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="T48" s="2" t="n"/>
+        <v>-3.8</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>28.6</v>
+      </c>
       <c r="U48" s="2" t="n">
-        <v>98</v>
+        <v>36.4</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="W48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X48" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="X48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5333,199 +5492,197 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>AAYUSHBULL</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>AAYUSH ART AND BULLION LIMITED</t>
+          <t>Krishana Phoschem Limited</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>1908</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="n">
+        <v>5895</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1245.9</v>
-      </c>
       <c r="J49" s="2" t="n">
-        <v>1247.65</v>
+        <v>190.68</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>8.68</v>
+        <v>190.68</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="N49" s="2" t="n">
-        <v>12.25</v>
+        <v>42.37</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>32.63</v>
+        <v>86.03</v>
       </c>
       <c r="P49" s="2" t="n">
+        <v>75.11</v>
+      </c>
+      <c r="Q49" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q49" s="2" t="n">
+      <c r="R49" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R49" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="S49" s="2" t="n">
-        <v>28.6</v>
-      </c>
+      <c r="S49" s="2" t="n"/>
       <c r="T49" s="2" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="U49" s="2" t="n">
-        <v>8</v>
-      </c>
+        <v>71.09999999999999</v>
+      </c>
+      <c r="U49" s="2" t="n"/>
       <c r="V49" s="2" t="n">
-        <v>8</v>
+        <v>196</v>
       </c>
       <c r="W49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="2" t="inlineStr">
+        <v>180</v>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Y49" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>KRISHANA</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Krishana Phoschem Limited</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>INVPRECQ</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Investment &amp; Precision Castings Limited</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
-        <v>5895</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>190.68</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>190.68</v>
-      </c>
-      <c r="K50" s="2" t="n">
+      <c r="F50" s="3" t="n">
+        <v>1217</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>1217.3</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>1217.3</v>
+      </c>
+      <c r="L50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n">
-        <v>42.37</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>86.03</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>75.11</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R50" s="2" t="n"/>
-      <c r="S50" s="2" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="T50" s="2" t="n"/>
-      <c r="U50" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="V50" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="W50" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="X50" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Y50" s="2" t="inlineStr">
+      <c r="N50" s="3" t="n"/>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S50" s="3" t="n"/>
+      <c r="T50" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="U50" s="3" t="n"/>
+      <c r="V50" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z50" s="2" t="inlineStr">
+      <c r="AA50" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5535,101 +5692,202 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
+          <t>DRAGARWQ</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Dr Agarwals Eye Hospital Limited</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>2611</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>5403</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>5418</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S51" s="2" t="n"/>
+      <c r="T51" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U51" s="2" t="n"/>
+      <c r="V51" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W51" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>NGLFINE</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>NGL Fine-Chem Limited</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F52" s="2" t="n">
         <v>2135</v>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="I52" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="J52" s="2" t="n">
         <v>3454</v>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="K52" s="2" t="n">
         <v>3457.8</v>
       </c>
-      <c r="K51" s="2" t="n">
+      <c r="L52" s="2" t="n">
         <v>-0.11</v>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="M51" s="2" t="n">
+      <c r="N52" s="2" t="n">
         <v>46.95</v>
       </c>
-      <c r="N51" s="2" t="n">
+      <c r="O52" s="2" t="n">
         <v>51.66</v>
       </c>
-      <c r="O51" s="2" t="n">
+      <c r="P52" s="2" t="n">
         <v>151.53</v>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="Q52" s="2" t="n">
         <v>4.03</v>
       </c>
-      <c r="Q51" s="2" t="n">
+      <c r="R52" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="R51" s="2" t="n"/>
-      <c r="S51" s="2" t="n">
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="n">
         <v>147.5</v>
       </c>
-      <c r="T51" s="2" t="n"/>
-      <c r="U51" s="2" t="n">
+      <c r="U52" s="2" t="n"/>
+      <c r="V52" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="V51" s="2" t="n">
+      <c r="W52" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="W51" s="2" t="n">
+      <c r="X52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X51" s="2" t="inlineStr">
+      <c r="Y52" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Y51" s="2" t="inlineStr">
+      <c r="Z52" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="Z51" s="2" t="inlineStr">
+      <c r="AA52" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
+      <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA51"/>
+  <autoFilter ref="A1:AB52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5648,80 +5906,80 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ATH Radar - weekly screen</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr"/>
+      <c r="B1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Run date</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>2026-08-15 (prices as of 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Universe</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2126 NSE mainboard (EQ) + 1014 NSE Emerge SME</t>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2378 NSE mainboard (EQ) + 1014 NSE Emerge SME</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Filters</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Within 2% of all-time-high close; TTM return above Nifty 500, Nifty Total Market, sector index (mainboard) / NIFTY SME EMERGE (SME); TTM PAT &gt;= every prior annual and rolling window (screener.in); mcap Rs 1,000-20,000 Cr</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Sort</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Newest entrant into the 2% ATH zone first; green rows new since previous run</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>3140 screened -&gt; 162 at ATH -&gt; 160 outperforming -&gt; 99 record PAT -&gt; 50 in mcap band</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>3392 screened -&gt; 181 at ATH -&gt; 174 outperforming -&gt; 103 record PAT -&gt; 51 in mcap band</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Caveats</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>SME price history since Jul-2024, unadjusted for corporate actions; PAT history limited to screener-visible years; mainboard prices split-adjusted (Yahoo). Factual screen - not investment advice</t>
         </is>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,13 +74,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4052,12 +4046,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Vadilal Industries Limited</t>
+          <t>Krishana Phoschem Limited</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4071,10 +4065,10 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>5572</v>
+        <v>5895</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>25.4</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -4085,27 +4079,27 @@
         <v>5</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7749</v>
+        <v>190.68</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>7781</v>
+        <v>190.68</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>-0.41</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="N35" s="2" t="n">
-        <v>84.89</v>
+        <v>42.37</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>50.78</v>
+        <v>86.03</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>58.01</v>
+        <v>75.11</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>4.03</v>
@@ -4115,21 +4109,21 @@
       </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="n">
-        <v>54</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="U35" s="2" t="n"/>
       <c r="V35" s="2" t="n">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>40.4</v>
+        <v>8.9</v>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4154,12 +4148,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>VADILALIND</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Kapston Services Limited</t>
+          <t>Vadilal Industries Limited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4173,41 +4167,41 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1791</v>
+        <v>5572</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>58.7</v>
+        <v>25.4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>588.4</v>
+        <v>7749</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>588.4</v>
+        <v>7781</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N36" s="2" t="n">
-        <v>79.5</v>
+        <v>84.89</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>49</v>
+        <v>50.78</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>140.29</v>
+        <v>58.01</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>4.03</v>
@@ -4217,17 +4211,17 @@
       </c>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="n">
-        <v>136.3</v>
+        <v>54</v>
       </c>
       <c r="U36" s="2" t="n"/>
       <c r="V36" s="2" t="n">
-        <v>30.5</v>
+        <v>219</v>
       </c>
       <c r="W36" s="2" t="n">
-        <v>28.1</v>
+        <v>156</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>8.5</v>
+        <v>40.4</v>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
@@ -4256,29 +4250,29 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>KAPSTON</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>Kapston Services Limited</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1399</v>
+        <v>1791</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>31.9</v>
+        <v>58.7</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -4289,10 +4283,10 @@
         <v>6</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>583</v>
+        <v>588.4</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>583</v>
+        <v>588.4</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -4303,13 +4297,13 @@
         </is>
       </c>
       <c r="N37" s="2" t="n">
-        <v>32.12</v>
+        <v>79.5</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>81.14</v>
+        <v>49</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>100.58</v>
+        <v>140.29</v>
       </c>
       <c r="Q37" s="2" t="n">
         <v>4.03</v>
@@ -4317,37 +4311,33 @@
       <c r="R37" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="S37" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+      <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="U37" s="2" t="n">
-        <v>104.4</v>
-      </c>
+        <v>136.3</v>
+      </c>
+      <c r="U37" s="2" t="n"/>
       <c r="V37" s="2" t="n">
-        <v>44</v>
+        <v>30.5</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>44</v>
+        <v>28.1</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4362,12 +4352,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>COMSYN</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>KSH International Limited</t>
+          <t>Commercial Syn Bags Limited</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4381,24 +4371,24 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6969</v>
+        <v>1163</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>53.2</v>
+        <v>39.2</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1028.6</v>
+        <v>288.33</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1028.6</v>
+        <v>288.33</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -4409,37 +4399,37 @@
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>61.92</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>184.97</v>
+        <v>58.46</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>189.75</v>
+        <v>103.74</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>-1.26</v>
+        <v>4.03</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-0.63</v>
+        <v>4.42</v>
       </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="n">
-        <v>191</v>
+        <v>99.7</v>
       </c>
       <c r="U38" s="2" t="n"/>
       <c r="V38" s="2" t="n">
-        <v>130</v>
+        <v>29.7</v>
       </c>
       <c r="W38" s="2" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>17.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4464,94 +4454,98 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SG Mart Limited</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>9274</v>
+        <v>1399</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>31.9</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>735.85</v>
+        <v>583</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>747.15</v>
+        <v>583</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-1.51</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>22.8</v>
+        <v>32.12</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>75.66</v>
+        <v>81.14</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>105.49</v>
+        <v>100.58</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>1.74</v>
+        <v>4.03</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S39" s="2" t="n"/>
+        <v>4.42</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="T39" s="2" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="U39" s="2" t="n"/>
+        <v>96.5</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>104.4</v>
+      </c>
       <c r="V39" s="2" t="n">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="W39" s="2" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -4566,12 +4560,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>COMSYN</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Commercial Syn Bags Limited</t>
+          <t>KSH International Limited</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4585,10 +4579,10 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1163</v>
+        <v>6969</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>39.2</v>
+        <v>53.2</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -4599,10 +4593,10 @@
         <v>9</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>288.33</v>
+        <v>1028.6</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>288.33</v>
+        <v>1028.6</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -4613,37 +4607,37 @@
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>61.92</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>58.46</v>
+        <v>184.97</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>103.74</v>
+        <v>189.75</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>4.03</v>
+        <v>-1.26</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>4.42</v>
+        <v>-0.63</v>
       </c>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="n">
-        <v>99.7</v>
+        <v>191</v>
       </c>
       <c r="U40" s="2" t="n"/>
       <c r="V40" s="2" t="n">
-        <v>29.7</v>
+        <v>130</v>
       </c>
       <c r="W40" s="2" t="n">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>6.1</v>
+        <v>17.1</v>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -4668,12 +4662,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited</t>
+          <t>SG Mart Limited</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4683,14 +4677,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>16077</v>
+        <v>9274</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>56.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -4701,51 +4695,47 @@
         <v>9</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>822</v>
+        <v>735.85</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>822</v>
+        <v>747.15</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>-1.51</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N41" s="2" t="n">
-        <v>71.81999999999999</v>
+        <v>22.8</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>151.53</v>
+        <v>75.66</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>80.93000000000001</v>
+        <v>105.49</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>4.03</v>
+        <v>1.74</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S41" s="2" t="n">
-        <v>12.7</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="U41" s="2" t="n">
-        <v>68.2</v>
-      </c>
+        <v>103.8</v>
+      </c>
+      <c r="U41" s="2" t="n"/>
       <c r="V41" s="2" t="n">
-        <v>298</v>
+        <v>125</v>
       </c>
       <c r="W41" s="2" t="n">
-        <v>244</v>
+        <v>120</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>22.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
@@ -4774,12 +4764,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>KDDL</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>KDDL Limited</t>
+          <t>Shilpa Medicare Limited</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4789,14 +4779,14 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>4834</v>
+        <v>16077</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>49.3</v>
+        <v>56.5</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -4807,27 +4797,27 @@
         <v>9</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3930.2</v>
+        <v>822</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3945.9</v>
+        <v>822</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>74.91</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>70.94</v>
+        <v>151.53</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>51.66</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>4.03</v>
@@ -4835,19 +4825,23 @@
       <c r="R42" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="S42" s="2" t="n"/>
+      <c r="S42" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="T42" s="2" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="U42" s="2" t="n"/>
+        <v>76.90000000000001</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>68.2</v>
+      </c>
       <c r="V42" s="2" t="n">
-        <v>151</v>
+        <v>298</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>3.4</v>
+        <v>22.1</v>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
@@ -4876,12 +4870,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>KDDL</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Limited</t>
+          <t>KDDL Limited</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4895,41 +4889,41 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>11430</v>
+        <v>4834</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>36.5</v>
+        <v>49.3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2474.6</v>
+        <v>3930.2</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2480.4</v>
+        <v>3945.9</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.4</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>48.04</v>
+        <v>74.91</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>56.02</v>
+        <v>70.94</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>96.90000000000001</v>
+        <v>51.66</v>
       </c>
       <c r="Q43" s="2" t="n">
         <v>4.03</v>
@@ -4939,17 +4933,17 @@
       </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="U43" s="2" t="n"/>
       <c r="V43" s="2" t="n">
-        <v>304</v>
+        <v>151</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="X43" s="2" t="n">
-        <v>12.2</v>
+        <v>3.4</v>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
@@ -4978,12 +4972,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Sudeep Pharma Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4993,73 +4987,67 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nifty Chemicals</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>12487</v>
+        <v>2611</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>34.3</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1105.55</v>
+        <v>5403</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1108.4</v>
+        <v>5418</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N44" s="2" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>65.40000000000001</v>
-      </c>
+        <v>6.85</v>
+      </c>
+      <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="n">
-        <v>42.81</v>
+        <v>12.85</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>-1.41</v>
+        <v>3.19</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="S44" s="2" t="n">
-        <v>6.68</v>
-      </c>
+        <v>3.72</v>
+      </c>
+      <c r="S44" s="2" t="n"/>
       <c r="T44" s="2" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U44" s="2" t="n">
-        <v>36.1</v>
-      </c>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="U44" s="2" t="n"/>
       <c r="V44" s="2" t="n">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="W44" s="2" t="n">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5084,12 +5072,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Happy Forgings Limited</t>
+          <t>Pearl Global Industries Limited</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5103,41 +5091,41 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>19721</v>
+        <v>11430</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>60.2</v>
+        <v>36.5</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2089.6</v>
+        <v>2474.6</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2089.6</v>
+        <v>2480.4</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>50.7</v>
+        <v>48.04</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>60.76</v>
+        <v>56.02</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>120.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q45" s="2" t="n">
         <v>4.03</v>
@@ -5147,17 +5135,17 @@
       </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="n">
-        <v>116.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U45" s="2" t="n"/>
       <c r="V45" s="2" t="n">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="X45" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
@@ -5186,12 +5174,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>Sudeep Pharma Limited</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5201,67 +5189,73 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Chemicals</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1382</v>
+        <v>12487</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>23.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>165.42</v>
+        <v>1105.55</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>166.77</v>
+        <v>1108.4</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="N46" s="2" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="O46" s="2" t="n"/>
+        <v>70.36</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>65.40000000000001</v>
+      </c>
       <c r="P46" s="2" t="n">
-        <v>46.35</v>
+        <v>42.81</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>11.16</v>
+        <v>-1.41</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="S46" s="2" t="n"/>
+        <v>-0.85</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>6.68</v>
+      </c>
       <c r="T46" s="2" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="U46" s="2" t="n"/>
+        <v>44.2</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>36.1</v>
+      </c>
       <c r="V46" s="2" t="n">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="W46" s="2" t="n">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="X46" s="2" t="n">
-        <v>16</v>
+        <v>5.7</v>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5286,12 +5280,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>GSPCROP</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>GSP Crop Science Limited</t>
+          <t>Happy Forgings Limited</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5305,59 +5299,61 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>2774</v>
+        <v>19721</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>26.5</v>
+        <v>60.2</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>596.25</v>
+        <v>2089.6</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>597.5</v>
+        <v>2089.6</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="N47" s="2" t="n">
-        <v>39.38</v>
-      </c>
-      <c r="O47" s="2" t="n"/>
+        <v>50.7</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>60.76</v>
+      </c>
       <c r="P47" s="2" t="n">
-        <v>67.37</v>
+        <v>120.9</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>12</v>
+        <v>4.03</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>12.8</v>
+        <v>4.42</v>
       </c>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="2" t="n">
-        <v>55.4</v>
+        <v>116.9</v>
       </c>
       <c r="U47" s="2" t="n"/>
       <c r="V47" s="2" t="n">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="W47" s="2" t="n">
-        <v>97</v>
+        <v>302</v>
       </c>
       <c r="X47" s="2" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
@@ -5386,85 +5382,79 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>AAYUSHBULL</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>AAYUSH ART AND BULLION LIMITED</t>
+          <t>Rajputana Stainless Limited</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1908</v>
+        <v>1382</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>242</v>
+        <v>23.5</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>165.42</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>166.77</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="U48" s="2" t="n"/>
+      <c r="V48" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="X48" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="J48" s="2" t="n">
-        <v>1245.9</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>1247.65</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>32.63</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S48" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="T48" s="2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="U48" s="2" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="V48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="X48" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
@@ -5472,12 +5462,12 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -5492,12 +5482,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>GSPCROP</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Krishana Phoschem Limited</t>
+          <t>GSP Crop Science Limited</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -5511,65 +5501,63 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>5895</v>
+        <v>2774</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>30</v>
+        <v>26.5</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>190.68</v>
+        <v>596.25</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>190.68</v>
+        <v>597.5</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="N49" s="2" t="n">
-        <v>42.37</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>86.03</v>
-      </c>
+        <v>39.38</v>
+      </c>
+      <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="n">
-        <v>75.11</v>
+        <v>67.37</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>4.03</v>
+        <v>12</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>4.42</v>
+        <v>12.8</v>
       </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="U49" s="2" t="n"/>
       <c r="V49" s="2" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="W49" s="2" t="n">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="X49" s="2" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -5589,100 +5577,108 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>INVPRECQ</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Investment &amp; Precision Castings Limited</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>1217</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>1217.3</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>1217.3</v>
-      </c>
-      <c r="L50" s="3" t="n">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>AAYUSHBULL</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>1908</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>1245.9</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>1247.65</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
-      <c r="P50" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="Q50" s="3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R50" s="3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S50" s="3" t="n"/>
-      <c r="T50" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="U50" s="3" t="n"/>
-      <c r="V50" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="W50" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="X50" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z50" s="3" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA50" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB50" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5692,17 +5688,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>INVPRECQ</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
+          <t>Investment &amp; Precision Castings Limited</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -5711,10 +5707,10 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>2611</v>
+        <v>1217</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>34.3</v>
+        <v>81.5</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -5725,23 +5721,23 @@
         <v>18</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5403</v>
+        <v>1217.3</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>5418</v>
+        <v>1217.3</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="N51" s="2" t="n"/>
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="n">
-        <v>7.34</v>
+        <v>31.8</v>
       </c>
       <c r="Q51" s="2" t="n">
         <v>1.94</v>
@@ -5751,21 +5747,21 @@
       </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="2" t="n">
-        <v>5.4</v>
+        <v>29.9</v>
       </c>
       <c r="U51" s="2" t="n"/>
       <c r="V51" s="2" t="n">
-        <v>75</v>
+        <v>14.6</v>
       </c>
       <c r="W51" s="2" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="X51" s="2" t="n">
-        <v>7.1</v>
+        <v>21.7</v>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -5820,7 +5816,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>3454</v>
@@ -5906,80 +5902,80 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ATH Radar - weekly screen</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr"/>
+      <c r="B1" s="4" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Run date</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>2026-08-15 (prices as of 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Universe</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>2378 NSE mainboard (EQ) + 1014 NSE Emerge SME</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Filters</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Within 2% of all-time-high close; TTM return above Nifty 500, Nifty Total Market, sector index (mainboard) / NIFTY SME EMERGE (SME); TTM PAT &gt;= every prior annual and rolling window (screener.in); mcap Rs 1,000-20,000 Cr</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Sort</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Newest entrant into the 2% ATH zone first; green rows new since previous run</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>3392 screened -&gt; 181 at ATH -&gt; 174 outperforming -&gt; 103 record PAT -&gt; 51 in mcap band</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>3392 screened -&gt; 172 at ATH -&gt; 169 outperforming -&gt; 103 record PAT -&gt; 51 in mcap band</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Caveats</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>SME price history since Jul-2024, unadjusted for corporate actions; PAT history limited to screener-visible years; mainboard prices split-adjusted (Yahoo). Factual screen - not investment advice</t>
         </is>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -4352,29 +4352,29 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>COMSYN</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Commercial Syn Bags Limited</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1163</v>
+        <v>1399</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>39.2</v>
+        <v>31.9</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -4385,10 +4385,10 @@
         <v>6</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>288.33</v>
+        <v>583</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>288.33</v>
+        <v>583</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>32.12</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>58.46</v>
+        <v>81.14</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>103.74</v>
+        <v>100.58</v>
       </c>
       <c r="Q38" s="2" t="n">
         <v>4.03</v>
@@ -4413,33 +4413,37 @@
       <c r="R38" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="S38" s="2" t="n"/>
+      <c r="S38" s="2" t="n">
+        <v>-3.8</v>
+      </c>
       <c r="T38" s="2" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="U38" s="2" t="n"/>
+        <v>96.5</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>104.4</v>
+      </c>
       <c r="V38" s="2" t="n">
-        <v>29.7</v>
+        <v>44</v>
       </c>
       <c r="W38" s="2" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4454,43 +4458,43 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>KSH International Limited</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>1399</v>
+        <v>6969</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>31.9</v>
+        <v>53.2</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>583</v>
+        <v>1028.6</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>583</v>
+        <v>1028.6</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -4501,37 +4505,33 @@
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>32.12</v>
+        <v>61.92</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>81.14</v>
+        <v>184.97</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>100.58</v>
+        <v>189.75</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>4.03</v>
+        <v>-1.26</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S39" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+        <v>-0.63</v>
+      </c>
+      <c r="S39" s="2" t="n"/>
       <c r="T39" s="2" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="U39" s="2" t="n">
-        <v>104.4</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="U39" s="2" t="n"/>
       <c r="V39" s="2" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="W39" s="2" t="n">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
@@ -4540,12 +4540,12 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>KSH International Limited</t>
+          <t>SG Mart Limited</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>6969</v>
+        <v>9274</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>53.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -4593,51 +4593,51 @@
         <v>9</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1028.6</v>
+        <v>735.85</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1028.6</v>
+        <v>747.15</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>-1.51</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>61.92</v>
+        <v>22.8</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>184.97</v>
+        <v>75.66</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>189.75</v>
+        <v>105.49</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>-1.26</v>
+        <v>1.74</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>-0.63</v>
+        <v>2.1</v>
       </c>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="n">
-        <v>191</v>
+        <v>103.8</v>
       </c>
       <c r="U40" s="2" t="n"/>
       <c r="V40" s="2" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="W40" s="2" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>17.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>COMSYN</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SG Mart Limited</t>
+          <t>Commercial Syn Bags Limited</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>9274</v>
+        <v>1163</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>39.2</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -4695,47 +4695,47 @@
         <v>9</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>735.85</v>
+        <v>288.33</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>747.15</v>
+        <v>288.33</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>-1.51</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="N41" s="2" t="n">
-        <v>22.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>75.66</v>
+        <v>58.46</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>105.49</v>
+        <v>103.74</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>1.74</v>
+        <v>4.03</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>2.1</v>
+        <v>4.42</v>
       </c>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="n">
-        <v>103.8</v>
+        <v>99.7</v>
       </c>
       <c r="U41" s="2" t="n"/>
       <c r="V41" s="2" t="n">
-        <v>125</v>
+        <v>29.7</v>
       </c>
       <c r="W41" s="2" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
@@ -5688,17 +5688,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>INVPRECQ</t>
+          <t>NGLFINE</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Investment &amp; Precision Castings Limited</t>
+          <t>NGL Fine-Chem Limited</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Main (T2T)</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -5707,57 +5707,61 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1217</v>
+        <v>2135</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>81.5</v>
+        <v>37.3</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1217.3</v>
+        <v>3454</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1217.3</v>
+        <v>3457.8</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="n"/>
-      <c r="O51" s="2" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>51.66</v>
+      </c>
       <c r="P51" s="2" t="n">
-        <v>31.8</v>
+        <v>151.53</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>1.94</v>
+        <v>4.03</v>
       </c>
       <c r="R51" s="2" t="n">
-        <v>2.06</v>
+        <v>4.42</v>
       </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="2" t="n">
-        <v>29.9</v>
+        <v>147.5</v>
       </c>
       <c r="U51" s="2" t="n"/>
       <c r="V51" s="2" t="n">
-        <v>14.6</v>
+        <v>57</v>
       </c>
       <c r="W51" s="2" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="X51" s="2" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
@@ -5786,17 +5790,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>NGLFINE</t>
+          <t>INVPRECQ</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>NGL Fine-Chem Limited</t>
+          <t>Investment &amp; Precision Castings Limited</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -5805,10 +5809,10 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>2135</v>
+        <v>1217</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>37.3</v>
+        <v>81.5</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -5819,47 +5823,45 @@
         <v>19</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3454</v>
+        <v>1217.3</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>3457.8</v>
+        <v>1217.3</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="N52" s="2" t="n">
-        <v>46.95</v>
-      </c>
-      <c r="O52" s="2" t="n">
-        <v>51.66</v>
-      </c>
+        <v>98.05</v>
+      </c>
+      <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="n">
-        <v>151.53</v>
+        <v>81.12</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>4.03</v>
+        <v>3.19</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>4.42</v>
+        <v>3.72</v>
       </c>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="2" t="n">
-        <v>147.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="U52" s="2" t="n"/>
       <c r="V52" s="2" t="n">
-        <v>57</v>
+        <v>14.6</v>
       </c>
       <c r="W52" s="2" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="X52" s="2" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
